--- a/research/traditional_assets/database/data/mauritius/mauritius_retail_building_supply.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_retail_building_supply.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1150314323100635</v>
+        <v>0.1148971351615984</v>
       </c>
       <c r="C2">
-        <v>323.012223680626</v>
+        <v>320.5706222421242</v>
       </c>
       <c r="D2">
-        <v>312.512223680626</v>
+        <v>313.1196222421242</v>
       </c>
       <c r="E2">
-        <v>-139.3</v>
+        <v>-136.251</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.049</v>
       </c>
       <c r="G2">
         <v>10.5</v>
@@ -1451,28 +1451,28 @@
         <v>28.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1533647</v>
       </c>
       <c r="N2">
-        <v>28.5</v>
+        <v>28.3466353</v>
       </c>
       <c r="O2">
-        <v>4.274999999999999</v>
+        <v>4.251995295</v>
       </c>
       <c r="P2">
-        <v>24.225</v>
+        <v>24.094640005</v>
       </c>
       <c r="Q2">
-        <v>26.225</v>
+        <v>26.094640005</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1150314323100635</v>
+        <v>0.1156258435975741</v>
       </c>
       <c r="T2">
-        <v>0.952996724804112</v>
+        <v>0.9611790199160664</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>185.8315505458557</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1148971351615984</v>
+        <v>0.1147628380131333</v>
       </c>
       <c r="C3">
-        <v>320.5706222421242</v>
+        <v>318.1313864804749</v>
       </c>
       <c r="D3">
-        <v>313.1196222421242</v>
+        <v>313.7293864804749</v>
       </c>
       <c r="E3">
-        <v>-136.251</v>
+        <v>-133.202</v>
       </c>
       <c r="F3">
-        <v>3.049</v>
+        <v>6.098</v>
       </c>
       <c r="G3">
         <v>10.5</v>
@@ -1533,28 +1533,28 @@
         <v>28.5</v>
       </c>
       <c r="M3">
-        <v>0.1533647</v>
+        <v>0.3067294</v>
       </c>
       <c r="N3">
-        <v>28.3466353</v>
+        <v>28.1932706</v>
       </c>
       <c r="O3">
-        <v>4.251995295</v>
+        <v>4.22899059</v>
       </c>
       <c r="P3">
-        <v>24.094640005</v>
+        <v>23.96428001</v>
       </c>
       <c r="Q3">
-        <v>26.094640005</v>
+        <v>25.96428001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1156258435975741</v>
+        <v>0.116232385727687</v>
       </c>
       <c r="T3">
-        <v>0.9611790199160664</v>
+        <v>0.9695283006425508</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>185.8315505458557</v>
+        <v>92.91577527292787</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1147628380131333</v>
+        <v>0.1146285408646682</v>
       </c>
       <c r="C4">
-        <v>318.1313864804749</v>
+        <v>315.6945302432909</v>
       </c>
       <c r="D4">
-        <v>313.7293864804749</v>
+        <v>314.3415302432909</v>
       </c>
       <c r="E4">
-        <v>-133.202</v>
+        <v>-130.153</v>
       </c>
       <c r="F4">
-        <v>6.098</v>
+        <v>9.146999999999998</v>
       </c>
       <c r="G4">
         <v>10.5</v>
@@ -1615,28 +1615,28 @@
         <v>28.5</v>
       </c>
       <c r="M4">
-        <v>0.3067294</v>
+        <v>0.4600940999999999</v>
       </c>
       <c r="N4">
-        <v>28.1932706</v>
+        <v>28.0399059</v>
       </c>
       <c r="O4">
-        <v>4.22899059</v>
+        <v>4.205985885</v>
       </c>
       <c r="P4">
-        <v>23.96428001</v>
+        <v>23.833920015</v>
       </c>
       <c r="Q4">
-        <v>25.96428001</v>
+        <v>25.833920015</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.116232385727687</v>
+        <v>0.1168514338811012</v>
       </c>
       <c r="T4">
-        <v>0.9695283006425508</v>
+        <v>0.9780497314871066</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>92.91577527292787</v>
+        <v>61.94385018195192</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1146285408646682</v>
+        <v>0.1144942437162031</v>
       </c>
       <c r="C5">
-        <v>315.6945302432909</v>
+        <v>313.2600674864729</v>
       </c>
       <c r="D5">
-        <v>314.3415302432909</v>
+        <v>314.9560674864729</v>
       </c>
       <c r="E5">
-        <v>-130.153</v>
+        <v>-127.104</v>
       </c>
       <c r="F5">
-        <v>9.146999999999998</v>
+        <v>12.196</v>
       </c>
       <c r="G5">
         <v>10.5</v>
@@ -1697,28 +1697,28 @@
         <v>28.5</v>
       </c>
       <c r="M5">
-        <v>0.4600940999999999</v>
+        <v>0.6134588</v>
       </c>
       <c r="N5">
-        <v>28.0399059</v>
+        <v>27.8865412</v>
       </c>
       <c r="O5">
-        <v>4.205985885</v>
+        <v>4.18298118</v>
       </c>
       <c r="P5">
-        <v>23.833920015</v>
+        <v>23.70356002</v>
       </c>
       <c r="Q5">
-        <v>25.833920015</v>
+        <v>25.70356002</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1168514338811012</v>
+        <v>0.1174833788710449</v>
       </c>
       <c r="T5">
-        <v>0.9780497314871066</v>
+        <v>0.9867486921409243</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>61.94385018195192</v>
+        <v>46.45788763646394</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1144942437162031</v>
+        <v>0.114359946567738</v>
       </c>
       <c r="C6">
-        <v>313.2600674864729</v>
+        <v>310.8280122752706</v>
       </c>
       <c r="D6">
-        <v>314.9560674864729</v>
+        <v>315.5730122752706</v>
       </c>
       <c r="E6">
-        <v>-127.104</v>
+        <v>-124.055</v>
       </c>
       <c r="F6">
-        <v>12.196</v>
+        <v>15.245</v>
       </c>
       <c r="G6">
         <v>10.5</v>
@@ -1779,28 +1779,28 @@
         <v>28.5</v>
       </c>
       <c r="M6">
-        <v>0.6134588</v>
+        <v>0.7668234999999999</v>
       </c>
       <c r="N6">
-        <v>27.8865412</v>
+        <v>27.7331765</v>
       </c>
       <c r="O6">
-        <v>4.18298118</v>
+        <v>4.159976475</v>
       </c>
       <c r="P6">
-        <v>23.70356002</v>
+        <v>23.573200025</v>
       </c>
       <c r="Q6">
-        <v>25.70356002</v>
+        <v>25.573200025</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1174833788710449</v>
+        <v>0.11812862796604</v>
       </c>
       <c r="T6">
-        <v>0.9867486921409243</v>
+        <v>0.9956307888085065</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.45788763646394</v>
+        <v>37.16631010917115</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.114359946567738</v>
+        <v>0.1142256494192729</v>
       </c>
       <c r="C7">
-        <v>310.8280122752706</v>
+        <v>308.3983787853555</v>
       </c>
       <c r="D7">
-        <v>315.5730122752706</v>
+        <v>316.1923787853555</v>
       </c>
       <c r="E7">
-        <v>-124.055</v>
+        <v>-121.006</v>
       </c>
       <c r="F7">
-        <v>15.245</v>
+        <v>18.294</v>
       </c>
       <c r="G7">
         <v>10.5</v>
@@ -1861,28 +1861,28 @@
         <v>28.5</v>
       </c>
       <c r="M7">
-        <v>0.7668234999999999</v>
+        <v>0.9201882</v>
       </c>
       <c r="N7">
-        <v>27.7331765</v>
+        <v>27.5798118</v>
       </c>
       <c r="O7">
-        <v>4.159976475</v>
+        <v>4.13697177</v>
       </c>
       <c r="P7">
-        <v>23.573200025</v>
+        <v>23.44284003</v>
       </c>
       <c r="Q7">
-        <v>25.573200025</v>
+        <v>25.44284003</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.11812862796604</v>
+        <v>0.1187876057651839</v>
       </c>
       <c r="T7">
-        <v>0.9956307888085065</v>
+        <v>1.00470186625625</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.16631010917115</v>
+        <v>30.97192509097595</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1142256494192729</v>
+        <v>0.1140913522708078</v>
       </c>
       <c r="C8">
-        <v>308.3983787853555</v>
+        <v>305.9711813039067</v>
       </c>
       <c r="D8">
-        <v>316.1923787853555</v>
+        <v>316.8141813039068</v>
       </c>
       <c r="E8">
-        <v>-121.006</v>
+        <v>-117.957</v>
       </c>
       <c r="F8">
-        <v>18.294</v>
+        <v>21.343</v>
       </c>
       <c r="G8">
         <v>10.5</v>
@@ -1943,28 +1943,28 @@
         <v>28.5</v>
       </c>
       <c r="M8">
-        <v>0.9201881999999998</v>
+        <v>1.0735529</v>
       </c>
       <c r="N8">
-        <v>27.5798118</v>
+        <v>27.4264471</v>
       </c>
       <c r="O8">
-        <v>4.13697177</v>
+        <v>4.113967065</v>
       </c>
       <c r="P8">
-        <v>23.44284003</v>
+        <v>23.312480035</v>
       </c>
       <c r="Q8">
-        <v>25.44284003</v>
+        <v>25.312480035</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1187876057651839</v>
+        <v>0.1194607551299009</v>
       </c>
       <c r="T8">
-        <v>1.00470186625625</v>
+        <v>1.013968020638354</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.97192509097596</v>
+        <v>26.54736436369368</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1140913522708078</v>
+        <v>0.1139570551223427</v>
       </c>
       <c r="C9">
-        <v>305.9711813039068</v>
+        <v>303.5464342307101</v>
       </c>
       <c r="D9">
-        <v>316.8141813039068</v>
+        <v>317.4384342307101</v>
       </c>
       <c r="E9">
-        <v>-117.957</v>
+        <v>-114.908</v>
       </c>
       <c r="F9">
-        <v>21.343</v>
+        <v>24.392</v>
       </c>
       <c r="G9">
         <v>10.5</v>
@@ -2025,28 +2025,28 @@
         <v>28.5</v>
       </c>
       <c r="M9">
-        <v>1.0735529</v>
+        <v>1.2269176</v>
       </c>
       <c r="N9">
-        <v>27.4264471</v>
+        <v>27.2730824</v>
       </c>
       <c r="O9">
-        <v>4.113967065</v>
+        <v>4.09096236</v>
       </c>
       <c r="P9">
-        <v>23.312480035</v>
+        <v>23.18212004</v>
       </c>
       <c r="Q9">
-        <v>25.312480035</v>
+        <v>25.18212004</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1194607551299009</v>
+        <v>0.1201485381764595</v>
       </c>
       <c r="T9">
-        <v>1.013968020638354</v>
+        <v>1.023435613159199</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.54736436369368</v>
+        <v>23.22894381823197</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1139570551223427</v>
+        <v>0.1138227579738776</v>
       </c>
       <c r="C10">
-        <v>303.5464342307101</v>
+        <v>301.1241520792688</v>
       </c>
       <c r="D10">
-        <v>317.4384342307101</v>
+        <v>318.0651520792688</v>
       </c>
       <c r="E10">
-        <v>-114.908</v>
+        <v>-111.859</v>
       </c>
       <c r="F10">
-        <v>24.392</v>
+        <v>27.441</v>
       </c>
       <c r="G10">
         <v>10.5</v>
@@ -2107,28 +2107,28 @@
         <v>28.5</v>
       </c>
       <c r="M10">
-        <v>1.2269176</v>
+        <v>1.3802823</v>
       </c>
       <c r="N10">
-        <v>27.2730824</v>
+        <v>27.1197177</v>
       </c>
       <c r="O10">
-        <v>4.09096236</v>
+        <v>4.067957655</v>
       </c>
       <c r="P10">
-        <v>23.18212004</v>
+        <v>23.051760045</v>
       </c>
       <c r="Q10">
-        <v>25.18212004</v>
+        <v>25.051760045</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1201485381764595</v>
+        <v>0.1208514373339314</v>
       </c>
       <c r="T10">
-        <v>1.023435613159199</v>
+        <v>1.033111284636546</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.22894381823197</v>
+        <v>20.64795006065064</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1138227579738776</v>
+        <v>0.1136884608254125</v>
       </c>
       <c r="C11">
-        <v>301.1241520792688</v>
+        <v>298.7043494779284</v>
       </c>
       <c r="D11">
-        <v>318.0651520792688</v>
+        <v>318.6943494779284</v>
       </c>
       <c r="E11">
-        <v>-111.859</v>
+        <v>-108.81</v>
       </c>
       <c r="F11">
-        <v>27.441</v>
+        <v>30.48999999999999</v>
       </c>
       <c r="G11">
         <v>10.5</v>
@@ -2189,28 +2189,28 @@
         <v>28.5</v>
       </c>
       <c r="M11">
-        <v>1.3802823</v>
+        <v>1.533647</v>
       </c>
       <c r="N11">
-        <v>27.1197177</v>
+        <v>26.966353</v>
       </c>
       <c r="O11">
-        <v>4.067957655</v>
+        <v>4.04495295</v>
       </c>
       <c r="P11">
-        <v>23.051760045</v>
+        <v>22.92140005</v>
       </c>
       <c r="Q11">
-        <v>25.051760045</v>
+        <v>24.92140005</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1208514373339314</v>
+        <v>0.1215699564726806</v>
       </c>
       <c r="T11">
-        <v>1.033111284636546</v>
+        <v>1.043001971035612</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.64795006065064</v>
+        <v>18.58315505458557</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1136884608254125</v>
+        <v>0.1135541636769474</v>
       </c>
       <c r="C12">
-        <v>298.7043494779284</v>
+        <v>296.287041171016</v>
       </c>
       <c r="D12">
-        <v>318.6943494779284</v>
+        <v>319.326041171016</v>
       </c>
       <c r="E12">
-        <v>-108.81</v>
+        <v>-105.761</v>
       </c>
       <c r="F12">
-        <v>30.49</v>
+        <v>33.53899999999999</v>
       </c>
       <c r="G12">
         <v>10.5</v>
@@ -2271,28 +2271,28 @@
         <v>28.5</v>
       </c>
       <c r="M12">
-        <v>1.533647</v>
+        <v>1.6870117</v>
       </c>
       <c r="N12">
-        <v>26.966353</v>
+        <v>26.8129883</v>
       </c>
       <c r="O12">
-        <v>4.04495295</v>
+        <v>4.021948245</v>
       </c>
       <c r="P12">
-        <v>22.92140005</v>
+        <v>22.791040055</v>
       </c>
       <c r="Q12">
-        <v>24.92140005</v>
+        <v>24.791040055</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1215699564726806</v>
+        <v>0.1223046221089297</v>
       </c>
       <c r="T12">
-        <v>1.043001971035612</v>
+        <v>1.053114920050387</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.58315505458557</v>
+        <v>16.89377732235052</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1135541636769474</v>
+        <v>0.1134198665284823</v>
       </c>
       <c r="C13">
-        <v>296.287041171016</v>
+        <v>293.8722420199907</v>
       </c>
       <c r="D13">
-        <v>319.326041171016</v>
+        <v>319.9602420199907</v>
       </c>
       <c r="E13">
-        <v>-105.761</v>
+        <v>-102.712</v>
       </c>
       <c r="F13">
-        <v>33.53899999999999</v>
+        <v>36.58799999999999</v>
       </c>
       <c r="G13">
         <v>10.5</v>
@@ -2353,28 +2353,28 @@
         <v>28.5</v>
       </c>
       <c r="M13">
-        <v>1.6870117</v>
+        <v>1.8403764</v>
       </c>
       <c r="N13">
-        <v>26.8129883</v>
+        <v>26.6596236</v>
       </c>
       <c r="O13">
-        <v>4.021948245</v>
+        <v>3.99894354</v>
       </c>
       <c r="P13">
-        <v>22.791040055</v>
+        <v>22.66068006</v>
       </c>
       <c r="Q13">
-        <v>24.791040055</v>
+        <v>24.66068006</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1223046221089297</v>
+        <v>0.1230559846914572</v>
       </c>
       <c r="T13">
-        <v>1.053114920050387</v>
+        <v>1.063457708815498</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.89377732235052</v>
+        <v>15.48596254548798</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1134198665284823</v>
+        <v>0.1132855693800172</v>
       </c>
       <c r="C14">
-        <v>293.8722420199907</v>
+        <v>291.4599670046096</v>
       </c>
       <c r="D14">
-        <v>319.9602420199907</v>
+        <v>320.5969670046096</v>
       </c>
       <c r="E14">
-        <v>-102.712</v>
+        <v>-99.66300000000001</v>
       </c>
       <c r="F14">
-        <v>36.58799999999999</v>
+        <v>39.637</v>
       </c>
       <c r="G14">
         <v>10.5</v>
@@ -2435,28 +2435,28 @@
         <v>28.5</v>
       </c>
       <c r="M14">
-        <v>1.8403764</v>
+        <v>1.9937411</v>
       </c>
       <c r="N14">
-        <v>26.6596236</v>
+        <v>26.5062589</v>
       </c>
       <c r="O14">
-        <v>3.99894354</v>
+        <v>3.975938835</v>
       </c>
       <c r="P14">
-        <v>22.66068006</v>
+        <v>22.530320065</v>
       </c>
       <c r="Q14">
-        <v>24.66068006</v>
+        <v>24.530320065</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1230559846914572</v>
+        <v>0.1238246199770313</v>
       </c>
       <c r="T14">
-        <v>1.063457708815498</v>
+        <v>1.074038262839577</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.48596254548798</v>
+        <v>14.29473465737352</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1132855693800172</v>
+        <v>0.1131512722315521</v>
       </c>
       <c r="C15">
-        <v>291.4599670046096</v>
+        <v>289.0502312241073</v>
       </c>
       <c r="D15">
-        <v>320.5969670046096</v>
+        <v>321.2362312241073</v>
       </c>
       <c r="E15">
-        <v>-99.66300000000001</v>
+        <v>-96.614</v>
       </c>
       <c r="F15">
-        <v>39.637</v>
+        <v>42.686</v>
       </c>
       <c r="G15">
         <v>10.5</v>
@@ -2517,28 +2517,28 @@
         <v>28.5</v>
       </c>
       <c r="M15">
-        <v>1.9937411</v>
+        <v>2.1471058</v>
       </c>
       <c r="N15">
-        <v>26.5062589</v>
+        <v>26.3528942</v>
       </c>
       <c r="O15">
-        <v>3.975938835</v>
+        <v>3.95293413</v>
       </c>
       <c r="P15">
-        <v>22.530320065</v>
+        <v>22.39996007</v>
       </c>
       <c r="Q15">
-        <v>24.530320065</v>
+        <v>24.39996007</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1238246199770313</v>
+        <v>0.1246111305018048</v>
       </c>
       <c r="T15">
-        <v>1.074038262839577</v>
+        <v>1.084864876259565</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.29473465737352</v>
+        <v>13.27368218184684</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1131512722315521</v>
+        <v>0.113208225083087</v>
       </c>
       <c r="C16">
-        <v>289.0502312241073</v>
+        <v>285.7298204376343</v>
       </c>
       <c r="D16">
-        <v>321.2362312241073</v>
+        <v>320.9648204376343</v>
       </c>
       <c r="E16">
-        <v>-96.614</v>
+        <v>-93.565</v>
       </c>
       <c r="F16">
-        <v>42.686</v>
+        <v>45.73500000000001</v>
       </c>
       <c r="G16">
         <v>10.5</v>
@@ -2599,45 +2599,45 @@
         <v>28.5</v>
       </c>
       <c r="M16">
-        <v>2.1471058</v>
+        <v>2.369073</v>
       </c>
       <c r="N16">
-        <v>26.3528942</v>
+        <v>26.130927</v>
       </c>
       <c r="O16">
-        <v>3.95293413</v>
+        <v>3.91963905</v>
       </c>
       <c r="P16">
-        <v>22.39996007</v>
+        <v>22.21128795</v>
       </c>
       <c r="Q16">
-        <v>24.39996007</v>
+        <v>24.21128795</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1246111305018048</v>
+        <v>0.125416147156573</v>
       </c>
       <c r="T16">
-        <v>1.084864876259565</v>
+        <v>1.095946233524729</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.15</v>
       </c>
       <c r="W16">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.27368218184684</v>
+        <v>12.03002186931344</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.113208225083087</v>
+        <v>0.113086677934622</v>
       </c>
       <c r="C17">
-        <v>285.7298204376343</v>
+        <v>283.2606136430547</v>
       </c>
       <c r="D17">
-        <v>320.9648204376343</v>
+        <v>321.5446136430547</v>
       </c>
       <c r="E17">
-        <v>-93.56500000000003</v>
+        <v>-90.51600000000002</v>
       </c>
       <c r="F17">
-        <v>45.73499999999999</v>
+        <v>48.784</v>
       </c>
       <c r="G17">
         <v>10.5</v>
@@ -2681,28 +2681,28 @@
         <v>28.5</v>
       </c>
       <c r="M17">
-        <v>2.369073</v>
+        <v>2.5270112</v>
       </c>
       <c r="N17">
-        <v>26.130927</v>
+        <v>25.9729888</v>
       </c>
       <c r="O17">
-        <v>3.91963905</v>
+        <v>3.89594832</v>
       </c>
       <c r="P17">
-        <v>22.21128795</v>
+        <v>22.07704048</v>
       </c>
       <c r="Q17">
-        <v>24.21128795</v>
+        <v>24.07704048</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.125416147156573</v>
+        <v>0.1262403308745499</v>
       </c>
       <c r="T17">
-        <v>1.095946233524729</v>
+        <v>1.10729143262954</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.03002186931344</v>
+        <v>11.27814550248135</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.113086677934622</v>
+        <v>0.1129651307861568</v>
       </c>
       <c r="C18">
-        <v>283.2606136430547</v>
+        <v>280.7935053245743</v>
       </c>
       <c r="D18">
-        <v>321.5446136430547</v>
+        <v>322.1265053245743</v>
       </c>
       <c r="E18">
-        <v>-90.51600000000002</v>
+        <v>-87.46700000000001</v>
       </c>
       <c r="F18">
-        <v>48.784</v>
+        <v>51.833</v>
       </c>
       <c r="G18">
         <v>10.5</v>
@@ -2763,28 +2763,28 @@
         <v>28.5</v>
       </c>
       <c r="M18">
-        <v>2.5270112</v>
+        <v>2.6849494</v>
       </c>
       <c r="N18">
-        <v>25.9729888</v>
+        <v>25.8150506</v>
       </c>
       <c r="O18">
-        <v>3.89594832</v>
+        <v>3.87225759</v>
       </c>
       <c r="P18">
-        <v>22.07704048</v>
+        <v>21.94279301</v>
       </c>
       <c r="Q18">
-        <v>24.07704048</v>
+        <v>23.94279301</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1262403308745499</v>
+        <v>0.1270843744411528</v>
       </c>
       <c r="T18">
-        <v>1.10729143262954</v>
+        <v>1.118910010026033</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.27814550248135</v>
+        <v>10.61472517880598</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1129651307861568</v>
+        <v>0.1128435836376917</v>
       </c>
       <c r="C19">
-        <v>280.7935053245743</v>
+        <v>278.3285068955346</v>
       </c>
       <c r="D19">
-        <v>322.1265053245743</v>
+        <v>322.7105068955346</v>
       </c>
       <c r="E19">
-        <v>-87.46700000000001</v>
+        <v>-84.41800000000001</v>
       </c>
       <c r="F19">
-        <v>51.833</v>
+        <v>54.88200000000001</v>
       </c>
       <c r="G19">
         <v>10.5</v>
@@ -2845,28 +2845,28 @@
         <v>28.5</v>
       </c>
       <c r="M19">
-        <v>2.6849494</v>
+        <v>2.8428876</v>
       </c>
       <c r="N19">
-        <v>25.8150506</v>
+        <v>25.6571124</v>
       </c>
       <c r="O19">
-        <v>3.87225759</v>
+        <v>3.84856686</v>
       </c>
       <c r="P19">
-        <v>21.94279301</v>
+        <v>21.80854554</v>
       </c>
       <c r="Q19">
-        <v>23.94279301</v>
+        <v>23.80854554</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1270843744411528</v>
+        <v>0.1279490044362094</v>
       </c>
       <c r="T19">
-        <v>1.118910010026033</v>
+        <v>1.130811967359026</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.61472517880598</v>
+        <v>10.02501822442787</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1128435836376917</v>
+        <v>0.1129965864892267</v>
       </c>
       <c r="C20">
-        <v>278.3285068955345</v>
+        <v>274.5447132050365</v>
       </c>
       <c r="D20">
-        <v>322.7105068955345</v>
+        <v>321.9757132050365</v>
       </c>
       <c r="E20">
-        <v>-84.41800000000002</v>
+        <v>-81.36900000000001</v>
       </c>
       <c r="F20">
-        <v>54.88199999999999</v>
+        <v>57.931</v>
       </c>
       <c r="G20">
         <v>10.5</v>
@@ -2927,45 +2927,45 @@
         <v>28.5</v>
       </c>
       <c r="M20">
-        <v>2.8428876</v>
+        <v>3.0993085</v>
       </c>
       <c r="N20">
-        <v>25.6571124</v>
+        <v>25.4006915</v>
       </c>
       <c r="O20">
-        <v>3.84856686</v>
+        <v>3.810103725</v>
       </c>
       <c r="P20">
-        <v>21.80854554</v>
+        <v>21.590587775</v>
       </c>
       <c r="Q20">
-        <v>23.80854554</v>
+        <v>23.590587775</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1279490044362094</v>
+        <v>0.1288349833200329</v>
       </c>
       <c r="T20">
-        <v>1.130811967359026</v>
+        <v>1.143007800181722</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.02501822442787</v>
+        <v>9.195599599071858</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1129965864892267</v>
+        <v>0.1128894893407615</v>
       </c>
       <c r="C21">
-        <v>274.5447132050365</v>
+        <v>272.0096935780892</v>
       </c>
       <c r="D21">
-        <v>321.9757132050365</v>
+        <v>322.4896935780892</v>
       </c>
       <c r="E21">
-        <v>-81.36900000000001</v>
+        <v>-78.32000000000002</v>
       </c>
       <c r="F21">
-        <v>57.931</v>
+        <v>60.98</v>
       </c>
       <c r="G21">
         <v>10.5</v>
@@ -3009,28 +3009,28 @@
         <v>28.5</v>
       </c>
       <c r="M21">
-        <v>3.0993085</v>
+        <v>3.26243</v>
       </c>
       <c r="N21">
-        <v>25.4006915</v>
+        <v>25.23757</v>
       </c>
       <c r="O21">
-        <v>3.810103725</v>
+        <v>3.7856355</v>
       </c>
       <c r="P21">
-        <v>21.590587775</v>
+        <v>21.4519345</v>
       </c>
       <c r="Q21">
-        <v>23.590587775</v>
+        <v>23.4519345</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1288349833200329</v>
+        <v>0.1297431116759519</v>
       </c>
       <c r="T21">
-        <v>1.143007800181722</v>
+        <v>1.155508528824986</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.195599599071858</v>
+        <v>8.735819619118267</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1128894893407615</v>
+        <v>0.1127823921922965</v>
       </c>
       <c r="C22">
-        <v>272.0096935780892</v>
+        <v>269.4763175422564</v>
       </c>
       <c r="D22">
-        <v>322.4896935780892</v>
+        <v>323.0053175422564</v>
       </c>
       <c r="E22">
-        <v>-78.32000000000002</v>
+        <v>-75.27100000000002</v>
       </c>
       <c r="F22">
-        <v>60.98</v>
+        <v>64.029</v>
       </c>
       <c r="G22">
         <v>10.5</v>
@@ -3091,28 +3091,28 @@
         <v>28.5</v>
       </c>
       <c r="M22">
-        <v>3.26243</v>
+        <v>3.4255515</v>
       </c>
       <c r="N22">
-        <v>25.23757</v>
+        <v>25.0744485</v>
       </c>
       <c r="O22">
-        <v>3.7856355</v>
+        <v>3.761167275</v>
       </c>
       <c r="P22">
-        <v>21.4519345</v>
+        <v>21.313281225</v>
       </c>
       <c r="Q22">
-        <v>23.4519345</v>
+        <v>23.313281225</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1297431116759519</v>
+        <v>0.1306742306231601</v>
       </c>
       <c r="T22">
-        <v>1.155508528824986</v>
+        <v>1.168325731611117</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.735819619118267</v>
+        <v>8.319828208684061</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1127823921922964</v>
+        <v>0.1126752950438314</v>
       </c>
       <c r="C23">
-        <v>269.4763175422565</v>
+        <v>266.9445929939036</v>
       </c>
       <c r="D23">
-        <v>323.0053175422565</v>
+        <v>323.5225929939036</v>
       </c>
       <c r="E23">
-        <v>-75.27100000000002</v>
+        <v>-72.22200000000002</v>
       </c>
       <c r="F23">
-        <v>64.029</v>
+        <v>67.07799999999999</v>
       </c>
       <c r="G23">
         <v>10.5</v>
@@ -3173,28 +3173,28 @@
         <v>28.5</v>
       </c>
       <c r="M23">
-        <v>3.4255515</v>
+        <v>3.588672999999999</v>
       </c>
       <c r="N23">
-        <v>25.0744485</v>
+        <v>24.911327</v>
       </c>
       <c r="O23">
-        <v>3.761167275</v>
+        <v>3.73669905</v>
       </c>
       <c r="P23">
-        <v>21.313281225</v>
+        <v>21.17462795</v>
       </c>
       <c r="Q23">
-        <v>23.313281225</v>
+        <v>23.17462795</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1306742306231601</v>
+        <v>0.1316292244151684</v>
       </c>
       <c r="T23">
-        <v>1.168325731611117</v>
+        <v>1.181471580622534</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.319828208684061</v>
+        <v>7.941654199198424</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1126752950438314</v>
+        <v>0.1127245978953663</v>
       </c>
       <c r="C24">
-        <v>266.9445929939036</v>
+        <v>263.6572563154299</v>
       </c>
       <c r="D24">
-        <v>323.5225929939036</v>
+        <v>323.28425631543</v>
       </c>
       <c r="E24">
-        <v>-72.22200000000002</v>
+        <v>-69.17300000000002</v>
       </c>
       <c r="F24">
-        <v>67.07799999999999</v>
+        <v>70.127</v>
       </c>
       <c r="G24">
         <v>10.5</v>
@@ -3255,45 +3255,45 @@
         <v>28.5</v>
       </c>
       <c r="M24">
-        <v>3.588672999999999</v>
+        <v>3.8078961</v>
       </c>
       <c r="N24">
-        <v>24.911327</v>
+        <v>24.6921039</v>
       </c>
       <c r="O24">
-        <v>3.73669905</v>
+        <v>3.703815585</v>
       </c>
       <c r="P24">
-        <v>21.17462795</v>
+        <v>20.988288315</v>
       </c>
       <c r="Q24">
-        <v>23.17462795</v>
+        <v>22.988288315</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1316292244151684</v>
+        <v>0.1326090232407354</v>
       </c>
       <c r="T24">
-        <v>1.181471580622534</v>
+        <v>1.194958880257623</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.15</v>
       </c>
       <c r="W24">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.941654199198424</v>
+        <v>7.484447908124384</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1127245978953663</v>
+        <v>0.1126243007469012</v>
       </c>
       <c r="C25">
-        <v>263.6572563154299</v>
+        <v>261.09347634302</v>
       </c>
       <c r="D25">
-        <v>323.28425631543</v>
+        <v>323.76947634302</v>
       </c>
       <c r="E25">
-        <v>-69.17300000000002</v>
+        <v>-66.12400000000001</v>
       </c>
       <c r="F25">
-        <v>70.127</v>
+        <v>73.176</v>
       </c>
       <c r="G25">
         <v>10.5</v>
@@ -3337,28 +3337,28 @@
         <v>28.5</v>
       </c>
       <c r="M25">
-        <v>3.8078961</v>
+        <v>3.9734568</v>
       </c>
       <c r="N25">
-        <v>24.6921039</v>
+        <v>24.5265432</v>
       </c>
       <c r="O25">
-        <v>3.703815585</v>
+        <v>3.67898148</v>
       </c>
       <c r="P25">
-        <v>20.988288315</v>
+        <v>20.84756172</v>
       </c>
       <c r="Q25">
-        <v>22.988288315</v>
+        <v>22.84756172</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1326090232407354</v>
+        <v>0.1336146062459226</v>
       </c>
       <c r="T25">
-        <v>1.194958880257623</v>
+        <v>1.208801108830479</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.484447908124384</v>
+        <v>7.172595911952534</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1126243007469012</v>
+        <v>0.1125240035984361</v>
       </c>
       <c r="C26">
-        <v>261.09347634302</v>
+        <v>258.531155101577</v>
       </c>
       <c r="D26">
-        <v>323.76947634302</v>
+        <v>324.256155101577</v>
       </c>
       <c r="E26">
-        <v>-66.12400000000002</v>
+        <v>-63.07500000000002</v>
       </c>
       <c r="F26">
-        <v>73.17599999999999</v>
+        <v>76.22499999999999</v>
       </c>
       <c r="G26">
         <v>10.5</v>
@@ -3419,28 +3419,28 @@
         <v>28.5</v>
       </c>
       <c r="M26">
-        <v>3.973456799999999</v>
+        <v>4.1390175</v>
       </c>
       <c r="N26">
-        <v>24.5265432</v>
+        <v>24.3609825</v>
       </c>
       <c r="O26">
-        <v>3.67898148</v>
+        <v>3.654147375</v>
       </c>
       <c r="P26">
-        <v>20.84756172</v>
+        <v>20.706835125</v>
       </c>
       <c r="Q26">
-        <v>22.84756172</v>
+        <v>22.706835125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1336146062459226</v>
+        <v>0.1346470047979148</v>
       </c>
       <c r="T26">
-        <v>1.208801108830479</v>
+        <v>1.22301246349861</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.172595911952536</v>
+        <v>6.885692075474434</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1125240035984361</v>
+        <v>0.112423706449971</v>
       </c>
       <c r="C27">
-        <v>258.531155101577</v>
+        <v>255.9702991791414</v>
       </c>
       <c r="D27">
-        <v>324.256155101577</v>
+        <v>324.7442991791414</v>
       </c>
       <c r="E27">
-        <v>-63.07500000000002</v>
+        <v>-60.02600000000001</v>
       </c>
       <c r="F27">
-        <v>76.22499999999999</v>
+        <v>79.274</v>
       </c>
       <c r="G27">
         <v>10.5</v>
@@ -3501,28 +3501,28 @@
         <v>28.5</v>
       </c>
       <c r="M27">
-        <v>4.1390175</v>
+        <v>4.3045782</v>
       </c>
       <c r="N27">
-        <v>24.3609825</v>
+        <v>24.1954218</v>
       </c>
       <c r="O27">
-        <v>3.654147375</v>
+        <v>3.629313269999999</v>
       </c>
       <c r="P27">
-        <v>20.706835125</v>
+        <v>20.56610853</v>
       </c>
       <c r="Q27">
-        <v>22.706835125</v>
+        <v>22.56610853</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1346470047979148</v>
+        <v>0.1357073060134743</v>
       </c>
       <c r="T27">
-        <v>1.22301246349861</v>
+        <v>1.237607908833448</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.885692075474434</v>
+        <v>6.620857764879262</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.112423706449971</v>
+        <v>0.1123234093015059</v>
       </c>
       <c r="C28">
-        <v>255.9702991791414</v>
+        <v>253.4109152034848</v>
       </c>
       <c r="D28">
-        <v>324.7442991791414</v>
+        <v>325.2339152034847</v>
       </c>
       <c r="E28">
-        <v>-60.02600000000001</v>
+        <v>-56.97700000000002</v>
       </c>
       <c r="F28">
-        <v>79.274</v>
+        <v>82.32299999999999</v>
       </c>
       <c r="G28">
         <v>10.5</v>
@@ -3583,28 +3583,28 @@
         <v>28.5</v>
       </c>
       <c r="M28">
-        <v>4.3045782</v>
+        <v>4.470138899999999</v>
       </c>
       <c r="N28">
-        <v>24.1954218</v>
+        <v>24.0298611</v>
       </c>
       <c r="O28">
-        <v>3.629313269999999</v>
+        <v>3.604479165</v>
       </c>
       <c r="P28">
-        <v>20.56610853</v>
+        <v>20.425381935</v>
       </c>
       <c r="Q28">
-        <v>22.56610853</v>
+        <v>22.425381935</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1357073060134743</v>
+        <v>0.1367966565774053</v>
       </c>
       <c r="T28">
-        <v>1.237607908833448</v>
+        <v>1.252603229382939</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.620857764879262</v>
+        <v>6.375640810624477</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1123234093015059</v>
+        <v>0.1122231121530408</v>
       </c>
       <c r="C29">
-        <v>253.4109152034848</v>
+        <v>250.8530098424093</v>
       </c>
       <c r="D29">
-        <v>325.2339152034847</v>
+        <v>325.7250098424093</v>
       </c>
       <c r="E29">
-        <v>-56.97700000000002</v>
+        <v>-53.92800000000001</v>
       </c>
       <c r="F29">
-        <v>82.32299999999999</v>
+        <v>85.372</v>
       </c>
       <c r="G29">
         <v>10.5</v>
@@ -3665,28 +3665,28 @@
         <v>28.5</v>
       </c>
       <c r="M29">
-        <v>4.470138899999999</v>
+        <v>4.6356996</v>
       </c>
       <c r="N29">
-        <v>24.0298611</v>
+        <v>23.8643004</v>
       </c>
       <c r="O29">
-        <v>3.604479165</v>
+        <v>3.57964506</v>
       </c>
       <c r="P29">
-        <v>20.425381935</v>
+        <v>20.28465534</v>
       </c>
       <c r="Q29">
-        <v>22.425381935</v>
+        <v>22.28465534</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1367966565774053</v>
+        <v>0.1379162668792233</v>
       </c>
       <c r="T29">
-        <v>1.252603229382939</v>
+        <v>1.26801508661436</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.375640810624477</v>
+        <v>6.147939353102173</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1122231121530408</v>
+        <v>0.1123693150045757</v>
       </c>
       <c r="C30">
-        <v>250.8530098424093</v>
+        <v>247.0886363215623</v>
       </c>
       <c r="D30">
-        <v>325.7250098424093</v>
+        <v>325.0096363215623</v>
       </c>
       <c r="E30">
-        <v>-53.92800000000001</v>
+        <v>-50.879</v>
       </c>
       <c r="F30">
-        <v>85.372</v>
+        <v>88.42100000000001</v>
       </c>
       <c r="G30">
         <v>10.5</v>
@@ -3747,45 +3747,45 @@
         <v>28.5</v>
       </c>
       <c r="M30">
-        <v>4.6356996</v>
+        <v>4.8896813</v>
       </c>
       <c r="N30">
-        <v>23.8643004</v>
+        <v>23.6103187</v>
       </c>
       <c r="O30">
-        <v>3.57964506</v>
+        <v>3.541547805</v>
       </c>
       <c r="P30">
-        <v>20.28465534</v>
+        <v>20.068770895</v>
       </c>
       <c r="Q30">
-        <v>22.28465534</v>
+        <v>22.068770895</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1379162668792233</v>
+        <v>0.1390674154994024</v>
       </c>
       <c r="T30">
-        <v>1.26801508661436</v>
+        <v>1.283861080669202</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.15</v>
       </c>
       <c r="W30">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.147939353102173</v>
+        <v>5.828600731094682</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1123693150045757</v>
+        <v>0.1122775178561106</v>
       </c>
       <c r="C31">
-        <v>247.0886363215623</v>
+        <v>244.4884340324302</v>
       </c>
       <c r="D31">
-        <v>325.0096363215623</v>
+        <v>325.4584340324301</v>
       </c>
       <c r="E31">
-        <v>-50.87900000000002</v>
+        <v>-47.83000000000003</v>
       </c>
       <c r="F31">
-        <v>88.42099999999999</v>
+        <v>91.46999999999998</v>
       </c>
       <c r="G31">
         <v>10.5</v>
@@ -3829,28 +3829,28 @@
         <v>28.5</v>
       </c>
       <c r="M31">
-        <v>4.889681299999999</v>
+        <v>5.058291</v>
       </c>
       <c r="N31">
-        <v>23.6103187</v>
+        <v>23.441709</v>
       </c>
       <c r="O31">
-        <v>3.541547805</v>
+        <v>3.51625635</v>
       </c>
       <c r="P31">
-        <v>20.068770895</v>
+        <v>19.92545265</v>
       </c>
       <c r="Q31">
-        <v>22.068770895</v>
+        <v>21.92545265</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1390674154994024</v>
+        <v>0.140251454080158</v>
       </c>
       <c r="T31">
-        <v>1.283861080669202</v>
+        <v>1.300159817411324</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.828600731094683</v>
+        <v>5.634314040058194</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1122775178561106</v>
+        <v>0.1121857207076455</v>
       </c>
       <c r="C32">
-        <v>244.4884340324302</v>
+        <v>241.889472924373</v>
       </c>
       <c r="D32">
-        <v>325.4584340324301</v>
+        <v>325.908472924373</v>
       </c>
       <c r="E32">
-        <v>-47.83000000000003</v>
+        <v>-44.78100000000002</v>
       </c>
       <c r="F32">
-        <v>91.46999999999998</v>
+        <v>94.51899999999999</v>
       </c>
       <c r="G32">
         <v>10.5</v>
@@ -3911,28 +3911,28 @@
         <v>28.5</v>
       </c>
       <c r="M32">
-        <v>5.058291</v>
+        <v>5.2269007</v>
       </c>
       <c r="N32">
-        <v>23.441709</v>
+        <v>23.2730993</v>
       </c>
       <c r="O32">
-        <v>3.51625635</v>
+        <v>3.490964895</v>
       </c>
       <c r="P32">
-        <v>19.92545265</v>
+        <v>19.782134405</v>
       </c>
       <c r="Q32">
-        <v>21.92545265</v>
+        <v>21.782134405</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.140251454080158</v>
+        <v>0.1414698126197761</v>
       </c>
       <c r="T32">
-        <v>1.300159817411324</v>
+        <v>1.316930981305392</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.634314040058194</v>
+        <v>5.452561974249865</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1121857207076455</v>
+        <v>0.1120939235591804</v>
       </c>
       <c r="C33">
-        <v>241.889472924373</v>
+        <v>239.2917581533785</v>
       </c>
       <c r="D33">
-        <v>325.908472924373</v>
+        <v>326.3597581533784</v>
       </c>
       <c r="E33">
-        <v>-44.78100000000002</v>
+        <v>-41.73200000000001</v>
       </c>
       <c r="F33">
-        <v>94.51899999999999</v>
+        <v>97.568</v>
       </c>
       <c r="G33">
         <v>10.5</v>
@@ -3993,28 +3993,28 @@
         <v>28.5</v>
       </c>
       <c r="M33">
-        <v>5.2269007</v>
+        <v>5.3955104</v>
       </c>
       <c r="N33">
-        <v>23.2730993</v>
+        <v>23.1044896</v>
       </c>
       <c r="O33">
-        <v>3.490964895</v>
+        <v>3.46567344</v>
       </c>
       <c r="P33">
-        <v>19.782134405</v>
+        <v>19.63881616</v>
       </c>
       <c r="Q33">
-        <v>21.782134405</v>
+        <v>21.63881616</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1414698126197761</v>
+        <v>0.1427240052340888</v>
       </c>
       <c r="T33">
-        <v>1.316930981305392</v>
+        <v>1.334195414725757</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.452561974249865</v>
+        <v>5.282169412554556</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1120939235591804</v>
+        <v>0.1120021264107153</v>
       </c>
       <c r="C34">
-        <v>239.2917581533785</v>
+        <v>236.6952949040317</v>
       </c>
       <c r="D34">
-        <v>326.3597581533784</v>
+        <v>326.8122949040317</v>
       </c>
       <c r="E34">
-        <v>-41.73200000000001</v>
+        <v>-38.68300000000002</v>
       </c>
       <c r="F34">
-        <v>97.568</v>
+        <v>100.617</v>
       </c>
       <c r="G34">
         <v>10.5</v>
@@ -4075,28 +4075,28 @@
         <v>28.5</v>
       </c>
       <c r="M34">
-        <v>5.3955104</v>
+        <v>5.564120099999999</v>
       </c>
       <c r="N34">
-        <v>23.1044896</v>
+        <v>22.9358799</v>
       </c>
       <c r="O34">
-        <v>3.46567344</v>
+        <v>3.440381985</v>
       </c>
       <c r="P34">
-        <v>19.63881616</v>
+        <v>19.495497915</v>
       </c>
       <c r="Q34">
-        <v>21.63881616</v>
+        <v>21.495497915</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1427240052340888</v>
+        <v>0.1440156364339034</v>
       </c>
       <c r="T34">
-        <v>1.334195414725757</v>
+        <v>1.351975204367625</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.282169412554556</v>
+        <v>5.122103672780177</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1120021264107153</v>
+        <v>0.1119103292622502</v>
       </c>
       <c r="C35">
-        <v>236.6952949040317</v>
+        <v>234.1000883897139</v>
       </c>
       <c r="D35">
-        <v>326.8122949040317</v>
+        <v>327.2660883897139</v>
       </c>
       <c r="E35">
-        <v>-38.68300000000002</v>
+        <v>-35.63400000000001</v>
       </c>
       <c r="F35">
-        <v>100.617</v>
+        <v>103.666</v>
       </c>
       <c r="G35">
         <v>10.5</v>
@@ -4157,28 +4157,28 @@
         <v>28.5</v>
       </c>
       <c r="M35">
-        <v>5.564120099999999</v>
+        <v>5.7327298</v>
       </c>
       <c r="N35">
-        <v>22.9358799</v>
+        <v>22.7672702</v>
       </c>
       <c r="O35">
-        <v>3.440381985</v>
+        <v>3.41509053</v>
       </c>
       <c r="P35">
-        <v>19.495497915</v>
+        <v>19.35217967</v>
       </c>
       <c r="Q35">
-        <v>21.495497915</v>
+        <v>21.35217967</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1440156364339034</v>
+        <v>0.1453464079731064</v>
       </c>
       <c r="T35">
-        <v>1.351975204367625</v>
+        <v>1.370293775513791</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.122103672780177</v>
+        <v>4.971453564757229</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1119103292622502</v>
+        <v>0.1118185321137851</v>
       </c>
       <c r="C36">
-        <v>234.1000883897139</v>
+        <v>231.5061438528031</v>
       </c>
       <c r="D36">
-        <v>327.2660883897139</v>
+        <v>327.7211438528031</v>
       </c>
       <c r="E36">
-        <v>-35.63400000000001</v>
+        <v>-32.58500000000001</v>
       </c>
       <c r="F36">
-        <v>103.666</v>
+        <v>106.715</v>
       </c>
       <c r="G36">
         <v>10.5</v>
@@ -4239,28 +4239,28 @@
         <v>28.5</v>
       </c>
       <c r="M36">
-        <v>5.7327298</v>
+        <v>5.901339500000001</v>
       </c>
       <c r="N36">
-        <v>22.7672702</v>
+        <v>22.5986605</v>
       </c>
       <c r="O36">
-        <v>3.41509053</v>
+        <v>3.389799075</v>
       </c>
       <c r="P36">
-        <v>19.35217967</v>
+        <v>19.208861425</v>
       </c>
       <c r="Q36">
-        <v>21.35217967</v>
+        <v>21.208861425</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1453464079731064</v>
+        <v>0.1467181263289002</v>
       </c>
       <c r="T36">
-        <v>1.370293775513791</v>
+        <v>1.389175995002917</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.971453564757229</v>
+        <v>4.829412034335594</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1118185321137851</v>
+        <v>0.11172673496532</v>
       </c>
       <c r="C37">
-        <v>231.5061438528031</v>
+        <v>228.9134665648747</v>
       </c>
       <c r="D37">
-        <v>327.7211438528031</v>
+        <v>328.1774665648747</v>
       </c>
       <c r="E37">
-        <v>-32.58500000000001</v>
+        <v>-29.536</v>
       </c>
       <c r="F37">
-        <v>106.715</v>
+        <v>109.764</v>
       </c>
       <c r="G37">
         <v>10.5</v>
@@ -4321,28 +4321,28 @@
         <v>28.5</v>
       </c>
       <c r="M37">
-        <v>5.901339500000001</v>
+        <v>6.069949200000001</v>
       </c>
       <c r="N37">
-        <v>22.5986605</v>
+        <v>22.4300508</v>
       </c>
       <c r="O37">
-        <v>3.389799075</v>
+        <v>3.36450762</v>
       </c>
       <c r="P37">
-        <v>19.208861425</v>
+        <v>19.06554318</v>
       </c>
       <c r="Q37">
-        <v>21.208861425</v>
+        <v>21.06554318</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1467181263289002</v>
+        <v>0.1481327108833126</v>
       </c>
       <c r="T37">
-        <v>1.389175995002917</v>
+        <v>1.408648283851078</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.829412034335594</v>
+        <v>4.695261700048494</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.11172673496532</v>
+        <v>0.1116349378168549</v>
       </c>
       <c r="C38">
-        <v>228.9134665648747</v>
+        <v>226.3220618269065</v>
       </c>
       <c r="D38">
-        <v>328.1774665648747</v>
+        <v>328.6350618269065</v>
       </c>
       <c r="E38">
-        <v>-29.53600000000003</v>
+        <v>-26.48700000000002</v>
       </c>
       <c r="F38">
-        <v>109.764</v>
+        <v>112.813</v>
       </c>
       <c r="G38">
         <v>10.5</v>
@@ -4403,28 +4403,28 @@
         <v>28.5</v>
       </c>
       <c r="M38">
-        <v>6.069949199999999</v>
+        <v>6.238558899999999</v>
       </c>
       <c r="N38">
-        <v>22.4300508</v>
+        <v>22.2614411</v>
       </c>
       <c r="O38">
-        <v>3.36450762</v>
+        <v>3.339216165</v>
       </c>
       <c r="P38">
-        <v>19.06554318</v>
+        <v>18.922224935</v>
       </c>
       <c r="Q38">
-        <v>21.06554318</v>
+        <v>20.922224935</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1481327108833126</v>
+        <v>0.1495922028838967</v>
       </c>
       <c r="T38">
-        <v>1.408648283851078</v>
+        <v>1.428738740599181</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.695261700048495</v>
+        <v>4.568362735182319</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1116349378168549</v>
+        <v>0.1123506406683898</v>
       </c>
       <c r="C39">
-        <v>226.3220618269065</v>
+        <v>219.738835131241</v>
       </c>
       <c r="D39">
-        <v>328.6350618269065</v>
+        <v>325.100835131241</v>
       </c>
       <c r="E39">
-        <v>-26.48700000000002</v>
+        <v>-23.43800000000002</v>
       </c>
       <c r="F39">
-        <v>112.813</v>
+        <v>115.862</v>
       </c>
       <c r="G39">
         <v>10.5</v>
@@ -4485,45 +4485,45 @@
         <v>28.5</v>
       </c>
       <c r="M39">
-        <v>6.238558899999999</v>
+        <v>6.6968236</v>
       </c>
       <c r="N39">
-        <v>22.2614411</v>
+        <v>21.8031764</v>
       </c>
       <c r="O39">
-        <v>3.339216165</v>
+        <v>3.27047646</v>
       </c>
       <c r="P39">
-        <v>18.922224935</v>
+        <v>18.53269994</v>
       </c>
       <c r="Q39">
-        <v>20.922224935</v>
+        <v>20.53269994</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1495922028838967</v>
+        <v>0.1510987752715965</v>
       </c>
       <c r="T39">
-        <v>1.428738740599181</v>
+        <v>1.449477276597222</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.15</v>
       </c>
       <c r="W39">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.568362735182319</v>
+        <v>4.255748949397443</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1123506406683898</v>
+        <v>0.1122800935199247</v>
       </c>
       <c r="C40">
-        <v>219.738835131241</v>
+        <v>217.034824671234</v>
       </c>
       <c r="D40">
-        <v>325.100835131241</v>
+        <v>325.445824671234</v>
       </c>
       <c r="E40">
-        <v>-23.43800000000002</v>
+        <v>-20.38900000000001</v>
       </c>
       <c r="F40">
-        <v>115.862</v>
+        <v>118.911</v>
       </c>
       <c r="G40">
         <v>10.5</v>
@@ -4567,28 +4567,28 @@
         <v>28.5</v>
       </c>
       <c r="M40">
-        <v>6.6968236</v>
+        <v>6.8730558</v>
       </c>
       <c r="N40">
-        <v>21.8031764</v>
+        <v>21.6269442</v>
       </c>
       <c r="O40">
-        <v>3.27047646</v>
+        <v>3.24404163</v>
       </c>
       <c r="P40">
-        <v>18.53269994</v>
+        <v>18.38290257</v>
       </c>
       <c r="Q40">
-        <v>20.53269994</v>
+        <v>20.38290257</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1510987752715965</v>
+        <v>0.1526547434752865</v>
       </c>
       <c r="T40">
-        <v>1.449477276597222</v>
+        <v>1.470895764595199</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.255748949397443</v>
+        <v>4.146627181464175</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1122800935199247</v>
+        <v>0.1122095463714596</v>
       </c>
       <c r="C41">
-        <v>217.034824671234</v>
+        <v>214.3315471789892</v>
       </c>
       <c r="D41">
-        <v>325.445824671234</v>
+        <v>325.7915471789892</v>
       </c>
       <c r="E41">
-        <v>-20.38900000000001</v>
+        <v>-17.34000000000002</v>
       </c>
       <c r="F41">
-        <v>118.911</v>
+        <v>121.96</v>
       </c>
       <c r="G41">
         <v>10.5</v>
@@ -4649,28 +4649,28 @@
         <v>28.5</v>
       </c>
       <c r="M41">
-        <v>6.8730558</v>
+        <v>7.049288</v>
       </c>
       <c r="N41">
-        <v>21.6269442</v>
+        <v>21.450712</v>
       </c>
       <c r="O41">
-        <v>3.24404163</v>
+        <v>3.2176068</v>
       </c>
       <c r="P41">
-        <v>18.38290257</v>
+        <v>18.2331052</v>
       </c>
       <c r="Q41">
-        <v>20.38290257</v>
+        <v>20.2331052</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1526547434752865</v>
+        <v>0.1542625772857661</v>
       </c>
       <c r="T41">
-        <v>1.470895764595199</v>
+        <v>1.493028202193109</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.146627181464175</v>
+        <v>4.042961501927571</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1122095463714596</v>
+        <v>0.1133587492229945</v>
       </c>
       <c r="C42">
-        <v>214.3315471789892</v>
+        <v>205.7406953932456</v>
       </c>
       <c r="D42">
-        <v>325.7915471789892</v>
+        <v>320.2496953932456</v>
       </c>
       <c r="E42">
-        <v>-17.34000000000002</v>
+        <v>-14.29100000000001</v>
       </c>
       <c r="F42">
-        <v>121.96</v>
+        <v>125.009</v>
       </c>
       <c r="G42">
         <v>10.5</v>
@@ -4731,45 +4731,45 @@
         <v>28.5</v>
       </c>
       <c r="M42">
-        <v>7.049288</v>
+        <v>7.6630517</v>
       </c>
       <c r="N42">
-        <v>21.450712</v>
+        <v>20.8369483</v>
       </c>
       <c r="O42">
-        <v>3.2176068</v>
+        <v>3.125542245</v>
       </c>
       <c r="P42">
-        <v>18.2331052</v>
+        <v>17.711406055</v>
       </c>
       <c r="Q42">
-        <v>20.2331052</v>
+        <v>19.711406055</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1542625772857661</v>
+        <v>0.1559249139372789</v>
       </c>
       <c r="T42">
-        <v>1.493028202193109</v>
+        <v>1.515910891912982</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.042961501927571</v>
+        <v>3.719144945870585</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1133587492229945</v>
+        <v>0.1133179520745295</v>
       </c>
       <c r="C43">
-        <v>205.7406953932456</v>
+        <v>202.8852035487424</v>
       </c>
       <c r="D43">
-        <v>320.2496953932456</v>
+        <v>320.4432035487424</v>
       </c>
       <c r="E43">
-        <v>-14.29100000000001</v>
+        <v>-11.24200000000002</v>
       </c>
       <c r="F43">
-        <v>125.009</v>
+        <v>128.058</v>
       </c>
       <c r="G43">
         <v>10.5</v>
@@ -4813,28 +4813,28 @@
         <v>28.5</v>
       </c>
       <c r="M43">
-        <v>7.6630517</v>
+        <v>7.8499554</v>
       </c>
       <c r="N43">
-        <v>20.8369483</v>
+        <v>20.6500446</v>
       </c>
       <c r="O43">
-        <v>3.125542245</v>
+        <v>3.09750669</v>
       </c>
       <c r="P43">
-        <v>17.711406055</v>
+        <v>17.55253791</v>
       </c>
       <c r="Q43">
-        <v>19.711406055</v>
+        <v>19.55253791</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1559249139372789</v>
+        <v>0.1576445725422922</v>
       </c>
       <c r="T43">
-        <v>1.515910891912982</v>
+        <v>1.539582639899057</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.719144945870585</v>
+        <v>3.63059387573081</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1133179520745295</v>
+        <v>0.1132771549260644</v>
       </c>
       <c r="C44">
-        <v>202.8852035487423</v>
+        <v>200.0299456969423</v>
       </c>
       <c r="D44">
-        <v>320.4432035487422</v>
+        <v>320.6369456969423</v>
       </c>
       <c r="E44">
-        <v>-11.24200000000002</v>
+        <v>-8.193000000000012</v>
       </c>
       <c r="F44">
-        <v>128.058</v>
+        <v>131.107</v>
       </c>
       <c r="G44">
         <v>10.5</v>
@@ -4895,28 +4895,28 @@
         <v>28.5</v>
       </c>
       <c r="M44">
-        <v>7.8499554</v>
+        <v>8.036859099999999</v>
       </c>
       <c r="N44">
-        <v>20.6500446</v>
+        <v>20.4631409</v>
       </c>
       <c r="O44">
-        <v>3.09750669</v>
+        <v>3.069471135</v>
       </c>
       <c r="P44">
-        <v>17.55253791</v>
+        <v>17.393669765</v>
       </c>
       <c r="Q44">
-        <v>19.55253791</v>
+        <v>19.393669765</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1576445725422922</v>
+        <v>0.159424570045727</v>
       </c>
       <c r="T44">
-        <v>1.539582639899057</v>
+        <v>1.564084975533766</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.63059387573081</v>
+        <v>3.54616146001614</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1132771549260644</v>
+        <v>0.1142835577775993</v>
       </c>
       <c r="C45">
-        <v>200.0299456969423</v>
+        <v>192.2690126880766</v>
       </c>
       <c r="D45">
-        <v>320.6369456969423</v>
+        <v>315.9250126880765</v>
       </c>
       <c r="E45">
-        <v>-8.193000000000012</v>
+        <v>-5.144000000000034</v>
       </c>
       <c r="F45">
-        <v>131.107</v>
+        <v>134.156</v>
       </c>
       <c r="G45">
         <v>10.5</v>
@@ -4977,45 +4977,45 @@
         <v>28.5</v>
       </c>
       <c r="M45">
-        <v>8.036859099999999</v>
+        <v>8.5993996</v>
       </c>
       <c r="N45">
-        <v>20.4631409</v>
+        <v>19.9006004</v>
       </c>
       <c r="O45">
-        <v>3.069471135</v>
+        <v>2.98509006</v>
       </c>
       <c r="P45">
-        <v>17.393669765</v>
+        <v>16.91551034</v>
       </c>
       <c r="Q45">
-        <v>19.393669765</v>
+        <v>18.91551034</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.159424570045727</v>
+        <v>0.1612681388885701</v>
       </c>
       <c r="T45">
-        <v>1.564084975533766</v>
+        <v>1.589462394584001</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.15</v>
       </c>
       <c r="W45">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.54616146001614</v>
+        <v>3.314184864720091</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1142835577775993</v>
+        <v>0.1142665606291342</v>
       </c>
       <c r="C46">
-        <v>192.2690126880766</v>
+        <v>189.2984425711487</v>
       </c>
       <c r="D46">
-        <v>315.9250126880765</v>
+        <v>316.0034425711487</v>
       </c>
       <c r="E46">
-        <v>-5.144000000000034</v>
+        <v>-2.095000000000027</v>
       </c>
       <c r="F46">
-        <v>134.156</v>
+        <v>137.205</v>
       </c>
       <c r="G46">
         <v>10.5</v>
@@ -5059,28 +5059,28 @@
         <v>28.5</v>
       </c>
       <c r="M46">
-        <v>8.5993996</v>
+        <v>8.794840499999999</v>
       </c>
       <c r="N46">
-        <v>19.9006004</v>
+        <v>19.7051595</v>
       </c>
       <c r="O46">
-        <v>2.98509006</v>
+        <v>2.955773925</v>
       </c>
       <c r="P46">
-        <v>16.91551034</v>
+        <v>16.749385575</v>
       </c>
       <c r="Q46">
-        <v>18.91551034</v>
+        <v>18.749385575</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1612681388885701</v>
+        <v>0.1631787465984258</v>
       </c>
       <c r="T46">
-        <v>1.589462394584001</v>
+        <v>1.615762628872426</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.314184864720091</v>
+        <v>3.240536312170756</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1142665606291342</v>
+        <v>0.1142495634806691</v>
       </c>
       <c r="C47">
-        <v>189.2984425711487</v>
+        <v>186.3279114050715</v>
       </c>
       <c r="D47">
-        <v>316.0034425711487</v>
+        <v>316.0819114050715</v>
       </c>
       <c r="E47">
-        <v>-2.095000000000027</v>
+        <v>0.9539999999999793</v>
       </c>
       <c r="F47">
-        <v>137.205</v>
+        <v>140.254</v>
       </c>
       <c r="G47">
         <v>10.5</v>
@@ -5141,28 +5141,28 @@
         <v>28.5</v>
       </c>
       <c r="M47">
-        <v>8.794840499999999</v>
+        <v>8.990281400000001</v>
       </c>
       <c r="N47">
-        <v>19.7051595</v>
+        <v>19.5097186</v>
       </c>
       <c r="O47">
-        <v>2.955773925</v>
+        <v>2.92645779</v>
       </c>
       <c r="P47">
-        <v>16.749385575</v>
+        <v>16.58326081</v>
       </c>
       <c r="Q47">
-        <v>18.749385575</v>
+        <v>18.58326081</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1631787465984258</v>
+        <v>0.1651601175567946</v>
       </c>
       <c r="T47">
-        <v>1.615762628872426</v>
+        <v>1.643036945912275</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.240536312170756</v>
+        <v>3.170089870601825</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1142495634806691</v>
+        <v>0.114232566332204</v>
       </c>
       <c r="C48">
-        <v>186.3279114050715</v>
+        <v>183.3574192188689</v>
       </c>
       <c r="D48">
-        <v>316.0819114050715</v>
+        <v>316.1604192188689</v>
       </c>
       <c r="E48">
-        <v>0.9539999999999793</v>
+        <v>4.002999999999986</v>
       </c>
       <c r="F48">
-        <v>140.254</v>
+        <v>143.303</v>
       </c>
       <c r="G48">
         <v>10.5</v>
@@ -5223,28 +5223,28 @@
         <v>28.5</v>
       </c>
       <c r="M48">
-        <v>8.990281400000001</v>
+        <v>9.1857223</v>
       </c>
       <c r="N48">
-        <v>19.5097186</v>
+        <v>19.3142777</v>
       </c>
       <c r="O48">
-        <v>2.92645779</v>
+        <v>2.897141655</v>
       </c>
       <c r="P48">
-        <v>16.58326081</v>
+        <v>16.417136045</v>
       </c>
       <c r="Q48">
-        <v>18.58326081</v>
+        <v>18.417136045</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1651601175567946</v>
+        <v>0.1672162572305736</v>
       </c>
       <c r="T48">
-        <v>1.643036945912275</v>
+        <v>1.671340482463061</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.170089870601825</v>
+        <v>3.102641149950723</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.114232566332204</v>
+        <v>0.1142155691837389</v>
       </c>
       <c r="C49">
-        <v>183.3574192188689</v>
+        <v>180.3869660415931</v>
       </c>
       <c r="D49">
-        <v>316.1604192188689</v>
+        <v>316.2389660415931</v>
       </c>
       <c r="E49">
-        <v>4.002999999999986</v>
+        <v>7.051999999999992</v>
       </c>
       <c r="F49">
-        <v>143.303</v>
+        <v>146.352</v>
       </c>
       <c r="G49">
         <v>10.5</v>
@@ -5305,28 +5305,28 @@
         <v>28.5</v>
       </c>
       <c r="M49">
-        <v>9.1857223</v>
+        <v>9.381163200000001</v>
       </c>
       <c r="N49">
-        <v>19.3142777</v>
+        <v>19.1188368</v>
       </c>
       <c r="O49">
-        <v>2.897141655</v>
+        <v>2.867825519999999</v>
       </c>
       <c r="P49">
-        <v>16.417136045</v>
+        <v>16.25101128</v>
       </c>
       <c r="Q49">
-        <v>18.417136045</v>
+        <v>18.25101128</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1672162572305736</v>
+        <v>0.1693514791994979</v>
       </c>
       <c r="T49">
-        <v>1.671340482463061</v>
+        <v>1.700732616573492</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.102641149950723</v>
+        <v>3.038002792660082</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1142155691837389</v>
+        <v>0.1174472720352738</v>
       </c>
       <c r="C50">
-        <v>180.3869660415933</v>
+        <v>163.0737751060344</v>
       </c>
       <c r="D50">
-        <v>316.2389660415932</v>
+        <v>301.9747751060344</v>
       </c>
       <c r="E50">
-        <v>7.051999999999964</v>
+        <v>10.10099999999997</v>
       </c>
       <c r="F50">
-        <v>146.352</v>
+        <v>149.401</v>
       </c>
       <c r="G50">
         <v>10.5</v>
@@ -5387,45 +5387,45 @@
         <v>28.5</v>
       </c>
       <c r="M50">
-        <v>9.3811632</v>
+        <v>10.7419319</v>
       </c>
       <c r="N50">
-        <v>19.1188368</v>
+        <v>17.7580681</v>
       </c>
       <c r="O50">
-        <v>2.86782552</v>
+        <v>2.663710215</v>
       </c>
       <c r="P50">
-        <v>16.25101128</v>
+        <v>15.094357885</v>
       </c>
       <c r="Q50">
-        <v>18.25101128</v>
+        <v>17.094357885</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1693514791994979</v>
+        <v>0.171570435363282</v>
       </c>
       <c r="T50">
-        <v>1.700732616573492</v>
+        <v>1.731277383394137</v>
       </c>
       <c r="U50">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V50">
         <v>0.15</v>
       </c>
       <c r="W50">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.038002792660083</v>
+        <v>2.653154038334576</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1174472720352738</v>
+        <v>0.1174965748868087</v>
       </c>
       <c r="C51">
-        <v>163.0737751060344</v>
+        <v>159.8171191960018</v>
       </c>
       <c r="D51">
-        <v>301.9747751060344</v>
+        <v>301.7671191960018</v>
       </c>
       <c r="E51">
-        <v>10.10099999999997</v>
+        <v>13.14999999999998</v>
       </c>
       <c r="F51">
-        <v>149.401</v>
+        <v>152.45</v>
       </c>
       <c r="G51">
         <v>10.5</v>
@@ -5469,28 +5469,28 @@
         <v>28.5</v>
       </c>
       <c r="M51">
-        <v>10.7419319</v>
+        <v>10.961155</v>
       </c>
       <c r="N51">
-        <v>17.7580681</v>
+        <v>17.538845</v>
       </c>
       <c r="O51">
-        <v>2.663710215</v>
+        <v>2.63082675</v>
       </c>
       <c r="P51">
-        <v>15.094357885</v>
+        <v>14.90801825</v>
       </c>
       <c r="Q51">
-        <v>17.094357885</v>
+        <v>16.90801825</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.171570435363282</v>
+        <v>0.1738781497736174</v>
       </c>
       <c r="T51">
-        <v>1.731277383394137</v>
+        <v>1.763043940887607</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.653154038334576</v>
+        <v>2.600090957567884</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1174965748868087</v>
+        <v>0.1175458777383436</v>
       </c>
       <c r="C52">
-        <v>159.8171191960018</v>
+        <v>156.5607486829516</v>
       </c>
       <c r="D52">
-        <v>301.7671191960018</v>
+        <v>301.5597486829516</v>
       </c>
       <c r="E52">
-        <v>13.14999999999998</v>
+        <v>16.19899999999998</v>
       </c>
       <c r="F52">
-        <v>152.45</v>
+        <v>155.499</v>
       </c>
       <c r="G52">
         <v>10.5</v>
@@ -5551,28 +5551,28 @@
         <v>28.5</v>
       </c>
       <c r="M52">
-        <v>10.961155</v>
+        <v>11.1803781</v>
       </c>
       <c r="N52">
-        <v>17.538845</v>
+        <v>17.3196219</v>
       </c>
       <c r="O52">
-        <v>2.63082675</v>
+        <v>2.597943285</v>
       </c>
       <c r="P52">
-        <v>14.90801825</v>
+        <v>14.721678615</v>
       </c>
       <c r="Q52">
-        <v>16.90801825</v>
+        <v>16.721678615</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1738781497736174</v>
+        <v>0.1762800566088645</v>
       </c>
       <c r="T52">
-        <v>1.763043940887607</v>
+        <v>1.796107092564485</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.600090957567884</v>
+        <v>2.549108781929298</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1175458777383436</v>
+        <v>0.1175951805898785</v>
       </c>
       <c r="C53">
-        <v>156.5607486829516</v>
+        <v>153.3046629789243</v>
       </c>
       <c r="D53">
-        <v>301.5597486829516</v>
+        <v>301.3526629789243</v>
       </c>
       <c r="E53">
-        <v>16.19899999999998</v>
+        <v>19.24799999999999</v>
       </c>
       <c r="F53">
-        <v>155.499</v>
+        <v>158.548</v>
       </c>
       <c r="G53">
         <v>10.5</v>
@@ -5633,28 +5633,28 @@
         <v>28.5</v>
       </c>
       <c r="M53">
-        <v>11.1803781</v>
+        <v>11.3996012</v>
       </c>
       <c r="N53">
-        <v>17.3196219</v>
+        <v>17.1003988</v>
       </c>
       <c r="O53">
-        <v>2.597943285</v>
+        <v>2.56505982</v>
       </c>
       <c r="P53">
-        <v>14.721678615</v>
+        <v>14.53533898</v>
       </c>
       <c r="Q53">
-        <v>16.721678615</v>
+        <v>16.53533898</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1762800566088645</v>
+        <v>0.1787820428955803</v>
       </c>
       <c r="T53">
-        <v>1.796107092564485</v>
+        <v>1.830547875561232</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.549108781929298</v>
+        <v>2.500087459199889</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1175951805898785</v>
+        <v>0.1194014334414134</v>
       </c>
       <c r="C54">
-        <v>153.3046629789243</v>
+        <v>142.8601669760293</v>
       </c>
       <c r="D54">
-        <v>301.3526629789243</v>
+        <v>293.9571669760293</v>
       </c>
       <c r="E54">
-        <v>19.24799999999999</v>
+        <v>22.297</v>
       </c>
       <c r="F54">
-        <v>158.548</v>
+        <v>161.597</v>
       </c>
       <c r="G54">
         <v>10.5</v>
@@ -5715,45 +5715,45 @@
         <v>28.5</v>
       </c>
       <c r="M54">
-        <v>11.3996012</v>
+        <v>12.2490526</v>
       </c>
       <c r="N54">
-        <v>17.1003988</v>
+        <v>16.2509474</v>
       </c>
       <c r="O54">
-        <v>2.56505982</v>
+        <v>2.43764211</v>
       </c>
       <c r="P54">
-        <v>14.53533898</v>
+        <v>13.81330529</v>
       </c>
       <c r="Q54">
-        <v>16.53533898</v>
+        <v>15.81330529</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1787820428955803</v>
+        <v>0.1813904966838583</v>
       </c>
       <c r="T54">
-        <v>1.830547875561232</v>
+        <v>1.866454223791883</v>
       </c>
       <c r="U54">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.15</v>
       </c>
       <c r="W54">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.500087459199889</v>
+        <v>2.326710557190357</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1194014334414134</v>
+        <v>0.1194838862929483</v>
       </c>
       <c r="C55">
-        <v>142.8601669760293</v>
+        <v>139.482226581247</v>
       </c>
       <c r="D55">
-        <v>293.9571669760293</v>
+        <v>293.628226581247</v>
       </c>
       <c r="E55">
-        <v>22.297</v>
+        <v>25.34599999999998</v>
       </c>
       <c r="F55">
-        <v>161.597</v>
+        <v>164.646</v>
       </c>
       <c r="G55">
         <v>10.5</v>
@@ -5797,28 +5797,28 @@
         <v>28.5</v>
       </c>
       <c r="M55">
-        <v>12.2490526</v>
+        <v>12.4801668</v>
       </c>
       <c r="N55">
-        <v>16.2509474</v>
+        <v>16.0198332</v>
       </c>
       <c r="O55">
-        <v>2.43764211</v>
+        <v>2.40297498</v>
       </c>
       <c r="P55">
-        <v>13.81330529</v>
+        <v>13.61685822</v>
       </c>
       <c r="Q55">
-        <v>15.81330529</v>
+        <v>15.61685822</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1813904966838583</v>
+        <v>0.1841123615064094</v>
       </c>
       <c r="T55">
-        <v>1.866454223791883</v>
+        <v>1.903921717597781</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.326710557190357</v>
+        <v>2.283623324649795</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1194838862929483</v>
+        <v>0.1195663391444832</v>
       </c>
       <c r="C56">
-        <v>139.482226581247</v>
+        <v>136.105021537408</v>
       </c>
       <c r="D56">
-        <v>293.628226581247</v>
+        <v>293.300021537408</v>
       </c>
       <c r="E56">
-        <v>25.34599999999998</v>
+        <v>28.39499999999998</v>
       </c>
       <c r="F56">
-        <v>164.646</v>
+        <v>167.695</v>
       </c>
       <c r="G56">
         <v>10.5</v>
@@ -5879,28 +5879,28 @@
         <v>28.5</v>
       </c>
       <c r="M56">
-        <v>12.4801668</v>
+        <v>12.711281</v>
       </c>
       <c r="N56">
-        <v>16.0198332</v>
+        <v>15.788719</v>
       </c>
       <c r="O56">
-        <v>2.40297498</v>
+        <v>2.36830785</v>
       </c>
       <c r="P56">
-        <v>13.61685822</v>
+        <v>13.42041115</v>
       </c>
       <c r="Q56">
-        <v>15.61685822</v>
+        <v>15.42041115</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1841123615064094</v>
+        <v>0.1869551980988516</v>
       </c>
       <c r="T56">
-        <v>1.903921717597781</v>
+        <v>1.943054433350607</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.283623324649795</v>
+        <v>2.242102900565254</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1195663391444832</v>
+        <v>0.1196487919960181</v>
       </c>
       <c r="C57">
-        <v>136.105021537408</v>
+        <v>132.728549381434</v>
       </c>
       <c r="D57">
-        <v>293.300021537408</v>
+        <v>292.972549381434</v>
       </c>
       <c r="E57">
-        <v>28.39499999999998</v>
+        <v>31.44399999999999</v>
       </c>
       <c r="F57">
-        <v>167.695</v>
+        <v>170.744</v>
       </c>
       <c r="G57">
         <v>10.5</v>
@@ -5961,28 +5961,28 @@
         <v>28.5</v>
       </c>
       <c r="M57">
-        <v>12.711281</v>
+        <v>12.9423952</v>
       </c>
       <c r="N57">
-        <v>15.788719</v>
+        <v>15.5576048</v>
       </c>
       <c r="O57">
-        <v>2.36830785</v>
+        <v>2.33364072</v>
       </c>
       <c r="P57">
-        <v>13.42041115</v>
+        <v>13.22396408</v>
       </c>
       <c r="Q57">
-        <v>15.42041115</v>
+        <v>15.22396408</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1869551980988516</v>
+        <v>0.1899272545364049</v>
       </c>
       <c r="T57">
-        <v>1.943054433350607</v>
+        <v>1.983965908910379</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.242102900565254</v>
+        <v>2.202065348769445</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1196487919960181</v>
+        <v>0.119731244847553</v>
       </c>
       <c r="C58">
-        <v>132.728549381434</v>
+        <v>129.3528076612349</v>
       </c>
       <c r="D58">
-        <v>292.972549381434</v>
+        <v>292.6458076612349</v>
       </c>
       <c r="E58">
-        <v>31.44399999999999</v>
+        <v>34.49299999999999</v>
       </c>
       <c r="F58">
-        <v>170.744</v>
+        <v>173.793</v>
       </c>
       <c r="G58">
         <v>10.5</v>
@@ -6043,28 +6043,28 @@
         <v>28.5</v>
       </c>
       <c r="M58">
-        <v>12.9423952</v>
+        <v>13.1735094</v>
       </c>
       <c r="N58">
-        <v>15.5576048</v>
+        <v>15.3264906</v>
       </c>
       <c r="O58">
-        <v>2.33364072</v>
+        <v>2.29897359</v>
       </c>
       <c r="P58">
-        <v>13.22396408</v>
+        <v>13.02751701</v>
       </c>
       <c r="Q58">
-        <v>15.22396408</v>
+        <v>15.02751701</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1899272545364049</v>
+        <v>0.1930375461571001</v>
       </c>
       <c r="T58">
-        <v>1.983965908910379</v>
+        <v>2.026780243798513</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.202065348769445</v>
+        <v>2.163432623352437</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.119731244847553</v>
+        <v>0.1198136976990879</v>
       </c>
       <c r="C59">
-        <v>129.3528076612349</v>
+        <v>125.9777939356472</v>
       </c>
       <c r="D59">
-        <v>292.6458076612349</v>
+        <v>292.3197939356472</v>
       </c>
       <c r="E59">
-        <v>34.49299999999999</v>
+        <v>37.542</v>
       </c>
       <c r="F59">
-        <v>173.793</v>
+        <v>176.842</v>
       </c>
       <c r="G59">
         <v>10.5</v>
@@ -6125,28 +6125,28 @@
         <v>28.5</v>
       </c>
       <c r="M59">
-        <v>13.1735094</v>
+        <v>13.4046236</v>
       </c>
       <c r="N59">
-        <v>15.3264906</v>
+        <v>15.0953764</v>
       </c>
       <c r="O59">
-        <v>2.29897359</v>
+        <v>2.264306459999999</v>
       </c>
       <c r="P59">
-        <v>13.02751701</v>
+        <v>12.83106994</v>
       </c>
       <c r="Q59">
-        <v>15.02751701</v>
+        <v>14.83106994</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1930375461571001</v>
+        <v>0.1962959469025903</v>
       </c>
       <c r="T59">
-        <v>2.026780243798513</v>
+        <v>2.071633356538463</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.163432623352437</v>
+        <v>2.126132060880844</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.119813697699088</v>
+        <v>0.1198961505506228</v>
       </c>
       <c r="C60">
-        <v>125.9777939356472</v>
+        <v>122.6035057743732</v>
       </c>
       <c r="D60">
-        <v>292.3197939356472</v>
+        <v>291.9945057743732</v>
       </c>
       <c r="E60">
-        <v>37.54199999999997</v>
+        <v>40.59099999999998</v>
       </c>
       <c r="F60">
-        <v>176.842</v>
+        <v>179.891</v>
       </c>
       <c r="G60">
         <v>10.5</v>
@@ -6207,28 +6207,28 @@
         <v>28.5</v>
       </c>
       <c r="M60">
-        <v>13.4046236</v>
+        <v>13.6357378</v>
       </c>
       <c r="N60">
-        <v>15.0953764</v>
+        <v>14.8642622</v>
       </c>
       <c r="O60">
-        <v>2.26430646</v>
+        <v>2.22963933</v>
       </c>
       <c r="P60">
-        <v>12.83106994</v>
+        <v>12.63462287</v>
       </c>
       <c r="Q60">
-        <v>14.83106994</v>
+        <v>14.63462287</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1962959469025903</v>
+        <v>0.1997132940259094</v>
       </c>
       <c r="T60">
-        <v>2.071633356538463</v>
+        <v>2.118674425997434</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.126132060880844</v>
+        <v>2.090095924255745</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1198961505506228</v>
+        <v>0.1199786034021577</v>
       </c>
       <c r="C61">
-        <v>122.6035057743732</v>
+        <v>119.2299407579211</v>
       </c>
       <c r="D61">
-        <v>291.9945057743732</v>
+        <v>291.6699407579211</v>
       </c>
       <c r="E61">
-        <v>40.59099999999998</v>
+        <v>43.63999999999996</v>
       </c>
       <c r="F61">
-        <v>179.891</v>
+        <v>182.94</v>
       </c>
       <c r="G61">
         <v>10.5</v>
@@ -6289,28 +6289,28 @@
         <v>28.5</v>
       </c>
       <c r="M61">
-        <v>13.6357378</v>
+        <v>13.866852</v>
       </c>
       <c r="N61">
-        <v>14.8642622</v>
+        <v>14.633148</v>
       </c>
       <c r="O61">
-        <v>2.22963933</v>
+        <v>2.1949722</v>
       </c>
       <c r="P61">
-        <v>12.63462287</v>
+        <v>12.4381758</v>
       </c>
       <c r="Q61">
-        <v>14.63462287</v>
+        <v>14.4381758</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1997132940259094</v>
+        <v>0.2033015085053943</v>
       </c>
       <c r="T61">
-        <v>2.118674425997434</v>
+        <v>2.168067548929354</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.090095924255745</v>
+        <v>2.055260992184817</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1199786034021577</v>
+        <v>0.1200610562536926</v>
       </c>
       <c r="C62">
-        <v>119.2299407579211</v>
+        <v>115.8570964775442</v>
       </c>
       <c r="D62">
-        <v>291.6699407579211</v>
+        <v>291.3460964775442</v>
       </c>
       <c r="E62">
-        <v>43.63999999999996</v>
+        <v>46.68899999999996</v>
       </c>
       <c r="F62">
-        <v>182.94</v>
+        <v>185.989</v>
       </c>
       <c r="G62">
         <v>10.5</v>
@@ -6371,28 +6371,28 @@
         <v>28.5</v>
       </c>
       <c r="M62">
-        <v>13.866852</v>
+        <v>14.0979662</v>
       </c>
       <c r="N62">
-        <v>14.633148</v>
+        <v>14.4020338</v>
       </c>
       <c r="O62">
-        <v>2.1949722</v>
+        <v>2.16030507</v>
       </c>
       <c r="P62">
-        <v>12.4381758</v>
+        <v>12.24172873</v>
       </c>
       <c r="Q62">
-        <v>14.4381758</v>
+        <v>14.24172873</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2033015085053943</v>
+        <v>0.2070737339838273</v>
       </c>
       <c r="T62">
-        <v>2.168067548929354</v>
+        <v>2.219993652524451</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.055260992184817</v>
+        <v>2.021568189034245</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1200610562536926</v>
+        <v>0.1276269091052276</v>
       </c>
       <c r="C63">
-        <v>115.8570964775442</v>
+        <v>85.86974919152439</v>
       </c>
       <c r="D63">
-        <v>291.3460964775442</v>
+        <v>264.4077491915244</v>
       </c>
       <c r="E63">
-        <v>46.68899999999996</v>
+        <v>49.73799999999997</v>
       </c>
       <c r="F63">
-        <v>185.989</v>
+        <v>189.038</v>
       </c>
       <c r="G63">
         <v>10.5</v>
@@ -6453,45 +6453,45 @@
         <v>28.5</v>
       </c>
       <c r="M63">
-        <v>14.0979662</v>
+        <v>17.01342</v>
       </c>
       <c r="N63">
-        <v>14.4020338</v>
+        <v>11.48658</v>
       </c>
       <c r="O63">
-        <v>2.16030507</v>
+        <v>1.722987</v>
       </c>
       <c r="P63">
-        <v>12.24172873</v>
+        <v>9.763593000000004</v>
       </c>
       <c r="Q63">
-        <v>14.24172873</v>
+        <v>11.763593</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2070737339838273</v>
+        <v>0.2110444976453357</v>
       </c>
       <c r="T63">
-        <v>2.219993652524451</v>
+        <v>2.274652708940341</v>
       </c>
       <c r="U63">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V63">
         <v>0.15</v>
       </c>
       <c r="W63">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.021568189034245</v>
+        <v>1.675148206533431</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1276269091052276</v>
+        <v>0.1278300619567624</v>
       </c>
       <c r="C64">
-        <v>85.86974919152439</v>
+        <v>82.16592598482617</v>
       </c>
       <c r="D64">
-        <v>264.4077491915244</v>
+        <v>263.7529259848262</v>
       </c>
       <c r="E64">
-        <v>49.73799999999997</v>
+        <v>52.78699999999998</v>
       </c>
       <c r="F64">
-        <v>189.038</v>
+        <v>192.087</v>
       </c>
       <c r="G64">
         <v>10.5</v>
@@ -6535,28 +6535,28 @@
         <v>28.5</v>
       </c>
       <c r="M64">
-        <v>17.01342</v>
+        <v>17.28783</v>
       </c>
       <c r="N64">
-        <v>11.48658</v>
+        <v>11.21217</v>
       </c>
       <c r="O64">
-        <v>1.722987</v>
+        <v>1.6818255</v>
       </c>
       <c r="P64">
-        <v>9.763593000000004</v>
+        <v>9.5303445</v>
       </c>
       <c r="Q64">
-        <v>11.763593</v>
+        <v>11.5303445</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2110444976453357</v>
+        <v>0.2152298971804391</v>
       </c>
       <c r="T64">
-        <v>2.274652708940341</v>
+        <v>2.332266308946279</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.675148206533431</v>
+        <v>1.648558552461472</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1278300619567624</v>
+        <v>0.1280332148082974</v>
       </c>
       <c r="C65">
-        <v>82.16592598482617</v>
+        <v>78.46533819102038</v>
       </c>
       <c r="D65">
-        <v>263.7529259848262</v>
+        <v>263.1013381910204</v>
       </c>
       <c r="E65">
-        <v>52.78699999999998</v>
+        <v>55.83599999999998</v>
       </c>
       <c r="F65">
-        <v>192.087</v>
+        <v>195.136</v>
       </c>
       <c r="G65">
         <v>10.5</v>
@@ -6617,28 +6617,28 @@
         <v>28.5</v>
       </c>
       <c r="M65">
-        <v>17.28783</v>
+        <v>17.56224</v>
       </c>
       <c r="N65">
-        <v>11.21217</v>
+        <v>10.93776</v>
       </c>
       <c r="O65">
-        <v>1.6818255</v>
+        <v>1.640664</v>
       </c>
       <c r="P65">
-        <v>9.5303445</v>
+        <v>9.297096</v>
       </c>
       <c r="Q65">
-        <v>11.5303445</v>
+        <v>11.297096</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2152298971804391</v>
+        <v>0.2196478189119371</v>
       </c>
       <c r="T65">
-        <v>2.332266308946279</v>
+        <v>2.393080664508104</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.648558552461472</v>
+        <v>1.622799825079261</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1280332148082974</v>
+        <v>0.1282363676598323</v>
       </c>
       <c r="C66">
-        <v>78.46533819102038</v>
+        <v>74.76796189044501</v>
       </c>
       <c r="D66">
-        <v>263.1013381910204</v>
+        <v>262.452961890445</v>
       </c>
       <c r="E66">
-        <v>55.83599999999998</v>
+        <v>58.88499999999999</v>
       </c>
       <c r="F66">
-        <v>195.136</v>
+        <v>198.185</v>
       </c>
       <c r="G66">
         <v>10.5</v>
@@ -6699,28 +6699,28 @@
         <v>28.5</v>
       </c>
       <c r="M66">
-        <v>17.56224</v>
+        <v>17.83665</v>
       </c>
       <c r="N66">
-        <v>10.93776</v>
+        <v>10.66335</v>
       </c>
       <c r="O66">
-        <v>1.640664</v>
+        <v>1.5995025</v>
       </c>
       <c r="P66">
-        <v>9.297096</v>
+        <v>9.063847500000001</v>
       </c>
       <c r="Q66">
-        <v>11.297096</v>
+        <v>11.0638475</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2196478189119371</v>
+        <v>0.2243181933138065</v>
       </c>
       <c r="T66">
-        <v>2.393080664508104</v>
+        <v>2.457370126102032</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.622799825079261</v>
+        <v>1.597833673924196</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1282363676598323</v>
+        <v>0.1284395205113672</v>
       </c>
       <c r="C67">
-        <v>74.76796189044501</v>
+        <v>71.07377339864473</v>
       </c>
       <c r="D67">
-        <v>262.452961890445</v>
+        <v>261.8077733986447</v>
       </c>
       <c r="E67">
-        <v>58.88499999999999</v>
+        <v>61.93399999999997</v>
       </c>
       <c r="F67">
-        <v>198.185</v>
+        <v>201.234</v>
       </c>
       <c r="G67">
         <v>10.5</v>
@@ -6781,28 +6781,28 @@
         <v>28.5</v>
       </c>
       <c r="M67">
-        <v>17.83665</v>
+        <v>18.11106</v>
       </c>
       <c r="N67">
-        <v>10.66335</v>
+        <v>10.38894</v>
       </c>
       <c r="O67">
-        <v>1.5995025</v>
+        <v>1.558341</v>
       </c>
       <c r="P67">
-        <v>9.063847500000001</v>
+        <v>8.830599000000001</v>
       </c>
       <c r="Q67">
-        <v>11.0638475</v>
+        <v>10.830599</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2243181933138065</v>
+        <v>0.2292632956216682</v>
       </c>
       <c r="T67">
-        <v>2.457370126102032</v>
+        <v>2.525441320730897</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.597833673924196</v>
+        <v>1.573624072804132</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1284395205113672</v>
+        <v>0.1286426733629021</v>
       </c>
       <c r="C68">
-        <v>71.07377339864473</v>
+        <v>67.3827492634874</v>
       </c>
       <c r="D68">
-        <v>261.8077733986447</v>
+        <v>261.1657492634874</v>
       </c>
       <c r="E68">
-        <v>61.93399999999997</v>
+        <v>64.98299999999998</v>
       </c>
       <c r="F68">
-        <v>201.234</v>
+        <v>204.283</v>
       </c>
       <c r="G68">
         <v>10.5</v>
@@ -6863,28 +6863,28 @@
         <v>28.5</v>
       </c>
       <c r="M68">
-        <v>18.11106</v>
+        <v>18.38547</v>
       </c>
       <c r="N68">
-        <v>10.38894</v>
+        <v>10.11453</v>
       </c>
       <c r="O68">
-        <v>1.558341</v>
+        <v>1.5171795</v>
       </c>
       <c r="P68">
-        <v>8.830599000000001</v>
+        <v>8.597350500000001</v>
       </c>
       <c r="Q68">
-        <v>10.830599</v>
+        <v>10.5973505</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2292632956216682</v>
+        <v>0.2345081010997033</v>
       </c>
       <c r="T68">
-        <v>2.525441320730897</v>
+        <v>2.597638042306966</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.573624072804132</v>
+        <v>1.550137146344369</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1286426733629021</v>
+        <v>0.128845826214437</v>
       </c>
       <c r="C69">
-        <v>67.3827492634874</v>
+        <v>63.69486626232214</v>
       </c>
       <c r="D69">
-        <v>261.1657492634874</v>
+        <v>260.5268662623221</v>
       </c>
       <c r="E69">
-        <v>64.98299999999998</v>
+        <v>68.03199999999998</v>
       </c>
       <c r="F69">
-        <v>204.283</v>
+        <v>207.332</v>
       </c>
       <c r="G69">
         <v>10.5</v>
@@ -6945,28 +6945,28 @@
         <v>28.5</v>
       </c>
       <c r="M69">
-        <v>18.38547</v>
+        <v>18.65988</v>
       </c>
       <c r="N69">
-        <v>10.11453</v>
+        <v>9.840120000000002</v>
       </c>
       <c r="O69">
-        <v>1.5171795</v>
+        <v>1.476018</v>
       </c>
       <c r="P69">
-        <v>8.597350500000001</v>
+        <v>8.364102000000003</v>
       </c>
       <c r="Q69">
-        <v>10.5973505</v>
+        <v>10.364102</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2345081010997033</v>
+        <v>0.2400807069201156</v>
       </c>
       <c r="T69">
-        <v>2.597638042306966</v>
+        <v>2.67434705898154</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.550137146344369</v>
+        <v>1.527341011839304</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.128845826214437</v>
+        <v>0.1290489790659719</v>
       </c>
       <c r="C70">
-        <v>63.69486626232214</v>
+        <v>60.01010139917943</v>
       </c>
       <c r="D70">
-        <v>260.5268662623221</v>
+        <v>259.8911013991794</v>
       </c>
       <c r="E70">
-        <v>68.03199999999998</v>
+        <v>71.08099999999999</v>
       </c>
       <c r="F70">
-        <v>207.332</v>
+        <v>210.381</v>
       </c>
       <c r="G70">
         <v>10.5</v>
@@ -7027,28 +7027,28 @@
         <v>28.5</v>
       </c>
       <c r="M70">
-        <v>18.65988</v>
+        <v>18.93429</v>
       </c>
       <c r="N70">
-        <v>9.840120000000002</v>
+        <v>9.565709999999999</v>
       </c>
       <c r="O70">
-        <v>1.476018</v>
+        <v>1.4348565</v>
       </c>
       <c r="P70">
-        <v>8.364102000000003</v>
+        <v>8.130853499999999</v>
       </c>
       <c r="Q70">
-        <v>10.364102</v>
+        <v>10.1308535</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2400807069201156</v>
+        <v>0.2460128356966836</v>
       </c>
       <c r="T70">
-        <v>2.67434705898154</v>
+        <v>2.756005044473828</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.527341011839304</v>
+        <v>1.505205634856126</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1290489790659719</v>
+        <v>0.1650980899553199</v>
       </c>
       <c r="C71">
-        <v>60.01010139917943</v>
+        <v>-21.5719508651332</v>
       </c>
       <c r="D71">
-        <v>259.8911013991794</v>
+        <v>181.3580491348668</v>
       </c>
       <c r="E71">
-        <v>71.08099999999999</v>
+        <v>74.13</v>
       </c>
       <c r="F71">
-        <v>210.381</v>
+        <v>213.43</v>
       </c>
       <c r="G71">
         <v>10.5</v>
@@ -7109,45 +7109,45 @@
         <v>28.5</v>
       </c>
       <c r="M71">
-        <v>18.93429</v>
+        <v>31.33152400000001</v>
       </c>
       <c r="N71">
-        <v>9.565709999999999</v>
+        <v>-2.831524000000005</v>
       </c>
       <c r="O71">
-        <v>1.4348565</v>
+        <v>-0.4247286000000008</v>
       </c>
       <c r="P71">
-        <v>8.130853499999999</v>
+        <v>-2.406795400000004</v>
       </c>
       <c r="Q71">
-        <v>10.1308535</v>
+        <v>-0.4067954000000045</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2460128356966836</v>
+        <v>0.2545302681466823</v>
       </c>
       <c r="T71">
-        <v>2.756005044473828</v>
+        <v>2.873250708152076</v>
       </c>
       <c r="U71">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.15</v>
+        <v>0.136444049130837</v>
       </c>
       <c r="W71">
-        <v>0.0765</v>
+        <v>0.1267700135875932</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.505205634856126</v>
+        <v>0.9096269942055801</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1650980899553199</v>
+        <v>0.1661080899553199</v>
       </c>
       <c r="C72">
-        <v>-21.5719508651332</v>
+        <v>-26.14347216602192</v>
       </c>
       <c r="D72">
-        <v>181.3580491348668</v>
+        <v>179.8355278339781</v>
       </c>
       <c r="E72">
-        <v>74.13</v>
+        <v>77.179</v>
       </c>
       <c r="F72">
-        <v>213.43</v>
+        <v>216.479</v>
       </c>
       <c r="G72">
         <v>10.5</v>
@@ -7191,37 +7191,37 @@
         <v>28.5</v>
       </c>
       <c r="M72">
-        <v>31.33152400000001</v>
+        <v>31.77911720000001</v>
       </c>
       <c r="N72">
-        <v>-2.831524000000005</v>
+        <v>-3.279117200000005</v>
       </c>
       <c r="O72">
-        <v>-0.4247286000000008</v>
+        <v>-0.4918675800000007</v>
       </c>
       <c r="P72">
-        <v>-2.406795400000004</v>
+        <v>-2.787249620000004</v>
       </c>
       <c r="Q72">
-        <v>-0.4067954000000045</v>
+        <v>-0.7872496200000043</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2545302681466823</v>
+        <v>0.2617278636000163</v>
       </c>
       <c r="T72">
-        <v>2.873250708152076</v>
+        <v>2.97232831877801</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.136444049130837</v>
+        <v>0.1345223019599802</v>
       </c>
       <c r="W72">
-        <v>0.1267700135875932</v>
+        <v>0.1270521260722749</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9096269942055801</v>
+        <v>0.8968153463998677</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1661080899553199</v>
+        <v>0.1671180899553199</v>
       </c>
       <c r="C73">
-        <v>-26.14347216602189</v>
+        <v>-30.68964281204188</v>
       </c>
       <c r="D73">
-        <v>179.8355278339781</v>
+        <v>178.3383571879581</v>
       </c>
       <c r="E73">
-        <v>77.17899999999997</v>
+        <v>80.22799999999995</v>
       </c>
       <c r="F73">
-        <v>216.479</v>
+        <v>219.528</v>
       </c>
       <c r="G73">
         <v>10.5</v>
@@ -7273,37 +7273,37 @@
         <v>28.5</v>
       </c>
       <c r="M73">
-        <v>31.7791172</v>
+        <v>32.22671039999999</v>
       </c>
       <c r="N73">
-        <v>-3.279117200000002</v>
+        <v>-3.726710399999995</v>
       </c>
       <c r="O73">
-        <v>-0.4918675800000002</v>
+        <v>-0.5590065599999992</v>
       </c>
       <c r="P73">
-        <v>-2.787249620000002</v>
+        <v>-3.167703839999995</v>
       </c>
       <c r="Q73">
-        <v>-0.7872496200000016</v>
+        <v>-1.167703839999995</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2617278636000162</v>
+        <v>0.2694395730143025</v>
       </c>
       <c r="T73">
-        <v>2.972328318778009</v>
+        <v>3.07848290159151</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1345223019599802</v>
+        <v>0.1326539366549805</v>
       </c>
       <c r="W73">
-        <v>0.1270521260722749</v>
+        <v>0.1273264020990489</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8968153463998678</v>
+        <v>0.8843595776998698</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1671180899553199</v>
+        <v>0.1681280899553199</v>
       </c>
       <c r="C74">
-        <v>-30.68964281204188</v>
+        <v>-35.21109072507332</v>
       </c>
       <c r="D74">
-        <v>178.3383571879581</v>
+        <v>176.8659092749267</v>
       </c>
       <c r="E74">
-        <v>80.22799999999995</v>
+        <v>83.27699999999996</v>
       </c>
       <c r="F74">
-        <v>219.528</v>
+        <v>222.577</v>
       </c>
       <c r="G74">
         <v>10.5</v>
@@ -7355,37 +7355,37 @@
         <v>28.5</v>
       </c>
       <c r="M74">
-        <v>32.22671039999999</v>
+        <v>32.6743036</v>
       </c>
       <c r="N74">
-        <v>-3.726710399999995</v>
+        <v>-4.174303600000002</v>
       </c>
       <c r="O74">
-        <v>-0.5590065599999992</v>
+        <v>-0.6261455400000002</v>
       </c>
       <c r="P74">
-        <v>-3.167703839999995</v>
+        <v>-3.548158060000001</v>
       </c>
       <c r="Q74">
-        <v>-1.167703839999995</v>
+        <v>-1.548158060000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2694395730143025</v>
+        <v>0.2777225201629803</v>
       </c>
       <c r="T74">
-        <v>3.07848290159151</v>
+        <v>3.192500786835639</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1326539366549805</v>
+        <v>0.1308367594405287</v>
       </c>
       <c r="W74">
-        <v>0.1273264020990489</v>
+        <v>0.1275931637141304</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8843595776998698</v>
+        <v>0.8722450629368578</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1681280899553199</v>
+        <v>0.1691380899553199</v>
       </c>
       <c r="C75">
-        <v>-35.21109072507332</v>
+        <v>-39.70842325910559</v>
       </c>
       <c r="D75">
-        <v>176.8659092749267</v>
+        <v>175.4175767408944</v>
       </c>
       <c r="E75">
-        <v>83.27699999999996</v>
+        <v>86.32599999999996</v>
       </c>
       <c r="F75">
-        <v>222.577</v>
+        <v>225.626</v>
       </c>
       <c r="G75">
         <v>10.5</v>
@@ -7437,37 +7437,37 @@
         <v>28.5</v>
       </c>
       <c r="M75">
-        <v>32.6743036</v>
+        <v>33.1218968</v>
       </c>
       <c r="N75">
-        <v>-4.174303600000002</v>
+        <v>-4.621896800000002</v>
       </c>
       <c r="O75">
-        <v>-0.6261455400000002</v>
+        <v>-0.6932845200000003</v>
       </c>
       <c r="P75">
-        <v>-3.548158060000001</v>
+        <v>-3.928612280000002</v>
       </c>
       <c r="Q75">
-        <v>-1.548158060000001</v>
+        <v>-1.928612280000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2777225201629803</v>
+        <v>0.2866426170923257</v>
       </c>
       <c r="T75">
-        <v>3.192500786835639</v>
+        <v>3.31528927863701</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1308367594405287</v>
+        <v>0.1290686951237648</v>
       </c>
       <c r="W75">
-        <v>0.1275931637141304</v>
+        <v>0.1278527155558314</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8722450629368578</v>
+        <v>0.8604579674917651</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1691380899553199</v>
+        <v>0.1701480899553199</v>
       </c>
       <c r="C76">
-        <v>-39.70842325910559</v>
+        <v>-44.18222803553567</v>
       </c>
       <c r="D76">
-        <v>175.4175767408944</v>
+        <v>173.9927719644643</v>
       </c>
       <c r="E76">
-        <v>86.32599999999996</v>
+        <v>89.37499999999997</v>
       </c>
       <c r="F76">
-        <v>225.626</v>
+        <v>228.675</v>
       </c>
       <c r="G76">
         <v>10.5</v>
@@ -7519,37 +7519,37 @@
         <v>28.5</v>
       </c>
       <c r="M76">
-        <v>33.1218968</v>
+        <v>33.56949</v>
       </c>
       <c r="N76">
-        <v>-4.621896800000002</v>
+        <v>-5.069490000000002</v>
       </c>
       <c r="O76">
-        <v>-0.6932845200000003</v>
+        <v>-0.7604235000000003</v>
       </c>
       <c r="P76">
-        <v>-3.928612280000002</v>
+        <v>-4.309066500000002</v>
       </c>
       <c r="Q76">
-        <v>-1.928612280000002</v>
+        <v>-2.309066500000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2866426170923257</v>
+        <v>0.2962763217760188</v>
       </c>
       <c r="T76">
-        <v>3.31528927863701</v>
+        <v>3.447900849782491</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1290686951237648</v>
+        <v>0.1273477791887812</v>
       </c>
       <c r="W76">
-        <v>0.1278527155558314</v>
+        <v>0.1281053460150869</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8604579674917651</v>
+        <v>0.8489851945918749</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1701480899553199</v>
+        <v>0.1711580899553199</v>
       </c>
       <c r="C77">
-        <v>-44.18222803553567</v>
+        <v>-48.63307373808857</v>
       </c>
       <c r="D77">
-        <v>173.9927719644643</v>
+        <v>172.5909262619114</v>
       </c>
       <c r="E77">
-        <v>89.37499999999997</v>
+        <v>92.42399999999998</v>
       </c>
       <c r="F77">
-        <v>228.675</v>
+        <v>231.724</v>
       </c>
       <c r="G77">
         <v>10.5</v>
@@ -7601,37 +7601,37 @@
         <v>28.5</v>
       </c>
       <c r="M77">
-        <v>33.56949</v>
+        <v>34.0170832</v>
       </c>
       <c r="N77">
-        <v>-5.069490000000002</v>
+        <v>-5.517083200000002</v>
       </c>
       <c r="O77">
-        <v>-0.7604235000000003</v>
+        <v>-0.8275624800000002</v>
       </c>
       <c r="P77">
-        <v>-4.309066500000002</v>
+        <v>-4.689520720000002</v>
       </c>
       <c r="Q77">
-        <v>-2.309066500000002</v>
+        <v>-2.689520720000002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2962763217760188</v>
+        <v>0.3067128351833529</v>
       </c>
       <c r="T77">
-        <v>3.447900849782491</v>
+        <v>3.591563385190095</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1273477791887812</v>
+        <v>0.1256721505152446</v>
       </c>
       <c r="W77">
-        <v>0.1281053460150869</v>
+        <v>0.1283513283043621</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8489851945918749</v>
+        <v>0.8378143367682975</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1711580899553199</v>
+        <v>0.1721680899553199</v>
       </c>
       <c r="C78">
-        <v>-48.63307373808857</v>
+        <v>-53.06151086961577</v>
       </c>
       <c r="D78">
-        <v>172.5909262619114</v>
+        <v>171.2114891303842</v>
       </c>
       <c r="E78">
-        <v>92.42399999999998</v>
+        <v>95.47299999999998</v>
       </c>
       <c r="F78">
-        <v>231.724</v>
+        <v>234.773</v>
       </c>
       <c r="G78">
         <v>10.5</v>
@@ -7683,37 +7683,37 @@
         <v>28.5</v>
       </c>
       <c r="M78">
-        <v>34.0170832</v>
+        <v>34.4646764</v>
       </c>
       <c r="N78">
-        <v>-5.517083200000002</v>
+        <v>-5.964676400000002</v>
       </c>
       <c r="O78">
-        <v>-0.8275624800000002</v>
+        <v>-0.8947014600000003</v>
       </c>
       <c r="P78">
-        <v>-4.689520720000002</v>
+        <v>-5.069974940000002</v>
       </c>
       <c r="Q78">
-        <v>-2.689520720000002</v>
+        <v>-3.069974940000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3067128351833529</v>
+        <v>0.3180568714956726</v>
       </c>
       <c r="T78">
-        <v>3.591563385190095</v>
+        <v>3.747718314980968</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1256721505152446</v>
+        <v>0.1240400446643973</v>
       </c>
       <c r="W78">
-        <v>0.1283513283043621</v>
+        <v>0.1285909214432665</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8378143367682975</v>
+        <v>0.8269336310959821</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1721680899553199</v>
+        <v>0.1731780899553199</v>
       </c>
       <c r="C79">
-        <v>-53.06151086961577</v>
+        <v>-57.4680724728895</v>
       </c>
       <c r="D79">
-        <v>171.2114891303842</v>
+        <v>169.8539275271105</v>
       </c>
       <c r="E79">
-        <v>95.47299999999998</v>
+        <v>98.52199999999999</v>
       </c>
       <c r="F79">
-        <v>234.773</v>
+        <v>237.822</v>
       </c>
       <c r="G79">
         <v>10.5</v>
@@ -7765,37 +7765,37 @@
         <v>28.5</v>
       </c>
       <c r="M79">
-        <v>34.4646764</v>
+        <v>34.9122696</v>
       </c>
       <c r="N79">
-        <v>-5.964676400000002</v>
+        <v>-6.412269600000002</v>
       </c>
       <c r="O79">
-        <v>-0.8947014600000003</v>
+        <v>-0.9618404400000002</v>
       </c>
       <c r="P79">
-        <v>-5.069974940000002</v>
+        <v>-5.450429160000001</v>
       </c>
       <c r="Q79">
-        <v>-3.069974940000002</v>
+        <v>-3.450429160000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3180568714956726</v>
+        <v>0.330432183836385</v>
       </c>
       <c r="T79">
-        <v>3.747718314980968</v>
+        <v>3.918069147480104</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1240400446643973</v>
+        <v>0.1224497876815204</v>
       </c>
       <c r="W79">
-        <v>0.1285909214432665</v>
+        <v>0.1288243711683528</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8269336310959821</v>
+        <v>0.8163319178768028</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1731780899553199</v>
+        <v>0.1741880899553199</v>
       </c>
       <c r="C80">
-        <v>-57.4680724728895</v>
+        <v>-61.85327481737554</v>
       </c>
       <c r="D80">
-        <v>169.8539275271105</v>
+        <v>168.5177251826244</v>
       </c>
       <c r="E80">
-        <v>98.52199999999999</v>
+        <v>101.571</v>
       </c>
       <c r="F80">
-        <v>237.822</v>
+        <v>240.871</v>
       </c>
       <c r="G80">
         <v>10.5</v>
@@ -7847,37 +7847,37 @@
         <v>28.5</v>
       </c>
       <c r="M80">
-        <v>34.9122696</v>
+        <v>35.3598628</v>
       </c>
       <c r="N80">
-        <v>-6.412269600000002</v>
+        <v>-6.859862800000002</v>
       </c>
       <c r="O80">
-        <v>-0.9618404400000002</v>
+        <v>-1.02897942</v>
       </c>
       <c r="P80">
-        <v>-5.450429160000001</v>
+        <v>-5.830883380000001</v>
       </c>
       <c r="Q80">
-        <v>-3.450429160000001</v>
+        <v>-3.830883380000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.330432183836385</v>
+        <v>0.3439860973524033</v>
       </c>
       <c r="T80">
-        <v>3.918069147480104</v>
+        <v>4.104643868788679</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1224497876815204</v>
+        <v>0.1208997903690961</v>
       </c>
       <c r="W80">
-        <v>0.1288243711683528</v>
+        <v>0.1290519107738167</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8163319178768028</v>
+        <v>0.8059986024606407</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1741880899553199</v>
+        <v>0.2201763120706943</v>
       </c>
       <c r="C81">
-        <v>-61.85327481737554</v>
+        <v>-109.3454132462596</v>
       </c>
       <c r="D81">
-        <v>168.5177251826244</v>
+        <v>124.0745867537404</v>
       </c>
       <c r="E81">
-        <v>101.571</v>
+        <v>104.62</v>
       </c>
       <c r="F81">
-        <v>240.871</v>
+        <v>243.92</v>
       </c>
       <c r="G81">
         <v>10.5</v>
@@ -7929,45 +7929,45 @@
         <v>28.5</v>
       </c>
       <c r="M81">
-        <v>35.3598628</v>
+        <v>48.979136</v>
       </c>
       <c r="N81">
-        <v>-6.859862800000002</v>
+        <v>-20.479136</v>
       </c>
       <c r="O81">
-        <v>-1.02897942</v>
+        <v>-3.071870399999999</v>
       </c>
       <c r="P81">
-        <v>-5.830883380000001</v>
+        <v>-17.4072656</v>
       </c>
       <c r="Q81">
-        <v>-3.830883380000001</v>
+        <v>-15.4072656</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3439860973524033</v>
+        <v>0.3677865127968954</v>
       </c>
       <c r="T81">
-        <v>4.104643868788679</v>
+        <v>4.432265545977079</v>
       </c>
       <c r="U81">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1208997903690961</v>
+        <v>0.08728206230505985</v>
       </c>
       <c r="W81">
-        <v>0.1290519107738167</v>
+        <v>0.183273761889144</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.8059986024606407</v>
+        <v>0.5818804153670657</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2201763120706943</v>
+        <v>0.2217263120706942</v>
       </c>
       <c r="C82">
-        <v>-109.3454132462596</v>
+        <v>-113.4875732585664</v>
       </c>
       <c r="D82">
-        <v>124.0745867537404</v>
+        <v>122.9814267414336</v>
       </c>
       <c r="E82">
-        <v>104.62</v>
+        <v>107.669</v>
       </c>
       <c r="F82">
-        <v>243.92</v>
+        <v>246.969</v>
       </c>
       <c r="G82">
         <v>10.5</v>
@@ -8011,37 +8011,37 @@
         <v>28.5</v>
       </c>
       <c r="M82">
-        <v>48.979136</v>
+        <v>49.5913752</v>
       </c>
       <c r="N82">
-        <v>-20.479136</v>
+        <v>-21.0913752</v>
       </c>
       <c r="O82">
-        <v>-3.071870399999999</v>
+        <v>-3.16370628</v>
       </c>
       <c r="P82">
-        <v>-17.4072656</v>
+        <v>-17.92766892</v>
       </c>
       <c r="Q82">
-        <v>-15.4072656</v>
+        <v>-15.92766892</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3677865127968954</v>
+        <v>0.384733171365153</v>
       </c>
       <c r="T82">
-        <v>4.432265545977079</v>
+        <v>4.665542679975872</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.08728206230505985</v>
+        <v>0.08620450598030603</v>
       </c>
       <c r="W82">
-        <v>0.183273761889144</v>
+        <v>0.1834901351991546</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5818804153670657</v>
+        <v>0.5746967065353734</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2217263120706942</v>
+        <v>0.2232763120706943</v>
       </c>
       <c r="C83">
-        <v>-113.4875732585664</v>
+        <v>-117.610638914006</v>
       </c>
       <c r="D83">
-        <v>122.9814267414336</v>
+        <v>121.907361085994</v>
       </c>
       <c r="E83">
-        <v>107.669</v>
+        <v>110.718</v>
       </c>
       <c r="F83">
-        <v>246.969</v>
+        <v>250.018</v>
       </c>
       <c r="G83">
         <v>10.5</v>
@@ -8093,37 +8093,37 @@
         <v>28.5</v>
       </c>
       <c r="M83">
-        <v>49.5913752</v>
+        <v>50.2036144</v>
       </c>
       <c r="N83">
-        <v>-21.0913752</v>
+        <v>-21.7036144</v>
       </c>
       <c r="O83">
-        <v>-3.16370628</v>
+        <v>-3.25554216</v>
       </c>
       <c r="P83">
-        <v>-17.92766892</v>
+        <v>-18.44807224</v>
       </c>
       <c r="Q83">
-        <v>-15.92766892</v>
+        <v>-16.44807224</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.384733171365153</v>
+        <v>0.4035627919965504</v>
       </c>
       <c r="T83">
-        <v>4.665542679975872</v>
+        <v>4.924739495530088</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.08620450598030603</v>
+        <v>0.08515323151713157</v>
       </c>
       <c r="W83">
-        <v>0.1834901351991546</v>
+        <v>0.18370123111136</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5746967065353734</v>
+        <v>0.5676882101142104</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2232763120706943</v>
+        <v>0.2248263120706943</v>
       </c>
       <c r="C84">
-        <v>-117.610638914006</v>
+        <v>-121.7151061662649</v>
       </c>
       <c r="D84">
-        <v>121.907361085994</v>
+        <v>120.8518938337351</v>
       </c>
       <c r="E84">
-        <v>110.718</v>
+        <v>113.767</v>
       </c>
       <c r="F84">
-        <v>250.018</v>
+        <v>253.067</v>
       </c>
       <c r="G84">
         <v>10.5</v>
@@ -8175,37 +8175,37 @@
         <v>28.5</v>
       </c>
       <c r="M84">
-        <v>50.2036144</v>
+        <v>50.8158536</v>
       </c>
       <c r="N84">
-        <v>-21.7036144</v>
+        <v>-22.3158536</v>
       </c>
       <c r="O84">
-        <v>-3.25554216</v>
+        <v>-3.347378040000001</v>
       </c>
       <c r="P84">
-        <v>-18.44807224</v>
+        <v>-18.96847556</v>
       </c>
       <c r="Q84">
-        <v>-16.44807224</v>
+        <v>-16.96847556</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4035627919965504</v>
+        <v>0.4246076621139946</v>
       </c>
       <c r="T84">
-        <v>4.924739495530088</v>
+        <v>5.214430054090682</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.08515323151713157</v>
+        <v>0.08412728896873238</v>
       </c>
       <c r="W84">
-        <v>0.18370123111136</v>
+        <v>0.1839072403750786</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5676882101142104</v>
+        <v>0.5608485931248826</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2248263120706943</v>
+        <v>0.2263763120706943</v>
       </c>
       <c r="C85">
-        <v>-121.7151061662649</v>
+        <v>-125.8014539407003</v>
       </c>
       <c r="D85">
-        <v>120.8518938337351</v>
+        <v>119.8145460592997</v>
       </c>
       <c r="E85">
-        <v>113.767</v>
+        <v>116.816</v>
       </c>
       <c r="F85">
-        <v>253.067</v>
+        <v>256.116</v>
       </c>
       <c r="G85">
         <v>10.5</v>
@@ -8257,37 +8257,37 @@
         <v>28.5</v>
       </c>
       <c r="M85">
-        <v>50.8158536</v>
+        <v>51.4280928</v>
       </c>
       <c r="N85">
-        <v>-22.3158536</v>
+        <v>-22.9280928</v>
       </c>
       <c r="O85">
-        <v>-3.347378040000001</v>
+        <v>-3.43921392</v>
       </c>
       <c r="P85">
-        <v>-18.96847556</v>
+        <v>-19.48887888</v>
       </c>
       <c r="Q85">
-        <v>-16.96847556</v>
+        <v>-17.48887888</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4246076621139946</v>
+        <v>0.4482831409961194</v>
       </c>
       <c r="T85">
-        <v>5.214430054090682</v>
+        <v>5.540331932471351</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.08412728896873238</v>
+        <v>0.08312577362386651</v>
       </c>
       <c r="W85">
-        <v>0.1839072403750786</v>
+        <v>0.1841083446563276</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5608485931248826</v>
+        <v>0.5541718241591101</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2263763120706943</v>
+        <v>0.2279263120706942</v>
       </c>
       <c r="C86">
-        <v>-125.8014539407003</v>
+        <v>-129.8701448589451</v>
       </c>
       <c r="D86">
-        <v>119.8145460592997</v>
+        <v>118.7948551410548</v>
       </c>
       <c r="E86">
-        <v>116.816</v>
+        <v>119.865</v>
       </c>
       <c r="F86">
-        <v>256.116</v>
+        <v>259.165</v>
       </c>
       <c r="G86">
         <v>10.5</v>
@@ -8339,37 +8339,37 @@
         <v>28.5</v>
       </c>
       <c r="M86">
-        <v>51.4280928</v>
+        <v>52.04033199999999</v>
       </c>
       <c r="N86">
-        <v>-22.9280928</v>
+        <v>-23.54033199999999</v>
       </c>
       <c r="O86">
-        <v>-3.43921392</v>
+        <v>-3.531049799999999</v>
       </c>
       <c r="P86">
-        <v>-19.48887888</v>
+        <v>-20.00928219999999</v>
       </c>
       <c r="Q86">
-        <v>-17.48887888</v>
+        <v>-18.00928219999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.448283140996119</v>
+        <v>0.4751153503958604</v>
       </c>
       <c r="T86">
-        <v>5.540331932471346</v>
+        <v>5.909687394636103</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.08312577362386651</v>
+        <v>0.0821478233459387</v>
       </c>
       <c r="W86">
-        <v>0.1841083446563276</v>
+        <v>0.1843047170721355</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5541718241591101</v>
+        <v>0.5476521556395912</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2279263120706942</v>
+        <v>0.2294763120706942</v>
       </c>
       <c r="C87">
-        <v>-129.8701448589451</v>
+        <v>-133.9216259268238</v>
       </c>
       <c r="D87">
-        <v>118.7948551410548</v>
+        <v>117.7923740731762</v>
       </c>
       <c r="E87">
-        <v>119.865</v>
+        <v>122.914</v>
       </c>
       <c r="F87">
-        <v>259.165</v>
+        <v>262.214</v>
       </c>
       <c r="G87">
         <v>10.5</v>
@@ -8421,37 +8421,37 @@
         <v>28.5</v>
       </c>
       <c r="M87">
-        <v>52.04033199999999</v>
+        <v>52.6525712</v>
       </c>
       <c r="N87">
-        <v>-23.54033199999999</v>
+        <v>-24.1525712</v>
       </c>
       <c r="O87">
-        <v>-3.531049799999999</v>
+        <v>-3.62288568</v>
       </c>
       <c r="P87">
-        <v>-20.00928219999999</v>
+        <v>-20.52968552</v>
       </c>
       <c r="Q87">
-        <v>-18.00928219999999</v>
+        <v>-18.52968552</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4751153503958604</v>
+        <v>0.5057807325669933</v>
       </c>
       <c r="T87">
-        <v>5.909687394636103</v>
+        <v>6.331807922824397</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.0821478233459387</v>
+        <v>0.0811926160977301</v>
       </c>
       <c r="W87">
-        <v>0.1843047170721355</v>
+        <v>0.1844965226875758</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5476521556395912</v>
+        <v>0.5412841073182006</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2294763120706942</v>
+        <v>0.2310263120706943</v>
       </c>
       <c r="C88">
-        <v>-133.9216259268238</v>
+        <v>-137.9563291877284</v>
       </c>
       <c r="D88">
-        <v>117.7923740731762</v>
+        <v>116.8066708122716</v>
       </c>
       <c r="E88">
-        <v>122.914</v>
+        <v>125.963</v>
       </c>
       <c r="F88">
-        <v>262.214</v>
+        <v>265.263</v>
       </c>
       <c r="G88">
         <v>10.5</v>
@@ -8503,37 +8503,37 @@
         <v>28.5</v>
       </c>
       <c r="M88">
-        <v>52.6525712</v>
+        <v>53.26481039999999</v>
       </c>
       <c r="N88">
-        <v>-24.1525712</v>
+        <v>-24.76481039999999</v>
       </c>
       <c r="O88">
-        <v>-3.62288568</v>
+        <v>-3.714721559999999</v>
       </c>
       <c r="P88">
-        <v>-20.52968552</v>
+        <v>-21.05008883999999</v>
       </c>
       <c r="Q88">
-        <v>-18.52968552</v>
+        <v>-19.05008883999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5057807325669933</v>
+        <v>0.5411638658413774</v>
       </c>
       <c r="T88">
-        <v>6.331807922824397</v>
+        <v>6.818870070733967</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.0811926160977301</v>
+        <v>0.08025936763683665</v>
       </c>
       <c r="W88">
-        <v>0.1844965226875758</v>
+        <v>0.1846839189785232</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5412841073182006</v>
+        <v>0.5350624509122444</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2310263120706943</v>
+        <v>0.2325763120706943</v>
       </c>
       <c r="C89">
-        <v>-137.9563291877284</v>
+        <v>-141.9746723434627</v>
       </c>
       <c r="D89">
-        <v>116.8066708122716</v>
+        <v>115.8373276565373</v>
       </c>
       <c r="E89">
-        <v>125.963</v>
+        <v>129.0119999999999</v>
       </c>
       <c r="F89">
-        <v>265.263</v>
+        <v>268.312</v>
       </c>
       <c r="G89">
         <v>10.5</v>
@@ -8585,37 +8585,37 @@
         <v>28.5</v>
       </c>
       <c r="M89">
-        <v>53.26481039999999</v>
+        <v>53.87704959999999</v>
       </c>
       <c r="N89">
-        <v>-24.76481039999999</v>
+        <v>-25.37704959999999</v>
       </c>
       <c r="O89">
-        <v>-3.714721559999999</v>
+        <v>-3.806557439999999</v>
       </c>
       <c r="P89">
-        <v>-21.05008883999999</v>
+        <v>-21.57049215999999</v>
       </c>
       <c r="Q89">
-        <v>-19.05008883999999</v>
+        <v>-19.57049215999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5411638658413774</v>
+        <v>0.5824441879948256</v>
       </c>
       <c r="T89">
-        <v>6.818870070733967</v>
+        <v>7.387109243295131</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08025936763683665</v>
+        <v>0.07934732936823623</v>
       </c>
       <c r="W89">
-        <v>0.1846839189785232</v>
+        <v>0.1848670562628582</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5350624509122444</v>
+        <v>0.5289821957882417</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2325763120706943</v>
+        <v>0.2341263120706942</v>
       </c>
       <c r="C90">
-        <v>-141.9746723434627</v>
+        <v>-145.9770593444264</v>
       </c>
       <c r="D90">
-        <v>115.8373276565373</v>
+        <v>114.8839406555736</v>
       </c>
       <c r="E90">
-        <v>129.0119999999999</v>
+        <v>132.061</v>
       </c>
       <c r="F90">
-        <v>268.312</v>
+        <v>271.361</v>
       </c>
       <c r="G90">
         <v>10.5</v>
@@ -8667,37 +8667,37 @@
         <v>28.5</v>
       </c>
       <c r="M90">
-        <v>53.87704959999999</v>
+        <v>54.4892888</v>
       </c>
       <c r="N90">
-        <v>-25.37704959999999</v>
+        <v>-25.9892888</v>
       </c>
       <c r="O90">
-        <v>-3.806557439999999</v>
+        <v>-3.898393319999999</v>
       </c>
       <c r="P90">
-        <v>-21.57049215999999</v>
+        <v>-22.09089548</v>
       </c>
       <c r="Q90">
-        <v>-19.57049215999999</v>
+        <v>-20.09089548</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5824441879948256</v>
+        <v>0.6312300232670823</v>
       </c>
       <c r="T90">
-        <v>7.387109243295131</v>
+        <v>8.058664629049233</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.07934732936823623</v>
+        <v>0.07845578634162682</v>
       </c>
       <c r="W90">
-        <v>0.1848670562628582</v>
+        <v>0.1850460781026013</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5289821957882417</v>
+        <v>0.5230385756108455</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2341263120706942</v>
+        <v>0.2356763120706943</v>
       </c>
       <c r="C91">
-        <v>-145.9770593444264</v>
+        <v>-149.9638809508932</v>
       </c>
       <c r="D91">
-        <v>114.8839406555736</v>
+        <v>113.9461190491067</v>
       </c>
       <c r="E91">
-        <v>132.061</v>
+        <v>135.11</v>
       </c>
       <c r="F91">
-        <v>271.361</v>
+        <v>274.41</v>
       </c>
       <c r="G91">
         <v>10.5</v>
@@ -8749,37 +8749,37 @@
         <v>28.5</v>
       </c>
       <c r="M91">
-        <v>54.4892888</v>
+        <v>55.10152799999999</v>
       </c>
       <c r="N91">
-        <v>-25.9892888</v>
+        <v>-26.60152799999999</v>
       </c>
       <c r="O91">
-        <v>-3.898393319999999</v>
+        <v>-3.990229199999999</v>
       </c>
       <c r="P91">
-        <v>-22.09089548</v>
+        <v>-22.6112988</v>
       </c>
       <c r="Q91">
-        <v>-20.09089548</v>
+        <v>-20.6112988</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6312300232670823</v>
+        <v>0.6897730255937907</v>
       </c>
       <c r="T91">
-        <v>8.058664629049233</v>
+        <v>8.864531091954158</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.07845578634162682</v>
+        <v>0.07758405538227542</v>
       </c>
       <c r="W91">
-        <v>0.1850460781026013</v>
+        <v>0.1852211216792391</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5230385756108455</v>
+        <v>0.5172270358818363</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2356763120706943</v>
+        <v>0.2372263120706943</v>
       </c>
       <c r="C92">
-        <v>-149.9638809508932</v>
+        <v>-153.9355152670205</v>
       </c>
       <c r="D92">
-        <v>113.9461190491067</v>
+        <v>113.0234847329795</v>
       </c>
       <c r="E92">
-        <v>135.11</v>
+        <v>138.159</v>
       </c>
       <c r="F92">
-        <v>274.41</v>
+        <v>277.459</v>
       </c>
       <c r="G92">
         <v>10.5</v>
@@ -8831,37 +8831,37 @@
         <v>28.5</v>
       </c>
       <c r="M92">
-        <v>55.10152799999999</v>
+        <v>55.7137672</v>
       </c>
       <c r="N92">
-        <v>-26.60152799999999</v>
+        <v>-27.2137672</v>
       </c>
       <c r="O92">
-        <v>-3.990229199999999</v>
+        <v>-4.08206508</v>
       </c>
       <c r="P92">
-        <v>-22.6112988</v>
+        <v>-23.13170212</v>
       </c>
       <c r="Q92">
-        <v>-20.6112988</v>
+        <v>-21.13170212</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6897730255937907</v>
+        <v>0.7613255839931008</v>
       </c>
       <c r="T92">
-        <v>8.864531091954158</v>
+        <v>9.849478991060176</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.07758405538227542</v>
+        <v>0.07673148334510757</v>
       </c>
       <c r="W92">
-        <v>0.1852211216792391</v>
+        <v>0.1853923181443024</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5172270358818363</v>
+        <v>0.511543222300717</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2372263120706943</v>
+        <v>0.2387763120706942</v>
       </c>
       <c r="C93">
-        <v>-153.9355152670205</v>
+        <v>-157.8923282491234</v>
       </c>
       <c r="D93">
-        <v>113.0234847329795</v>
+        <v>112.1156717508765</v>
       </c>
       <c r="E93">
-        <v>138.159</v>
+        <v>141.208</v>
       </c>
       <c r="F93">
-        <v>277.459</v>
+        <v>280.508</v>
       </c>
       <c r="G93">
         <v>10.5</v>
@@ -8913,37 +8913,37 @@
         <v>28.5</v>
       </c>
       <c r="M93">
-        <v>55.7137672</v>
+        <v>56.3260064</v>
       </c>
       <c r="N93">
-        <v>-27.2137672</v>
+        <v>-27.8260064</v>
       </c>
       <c r="O93">
-        <v>-4.08206508</v>
+        <v>-4.173900959999999</v>
       </c>
       <c r="P93">
-        <v>-23.13170212</v>
+        <v>-23.65210544</v>
       </c>
       <c r="Q93">
-        <v>-21.13170212</v>
+        <v>-21.65210544</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7613255839931008</v>
+        <v>0.8507662819922387</v>
       </c>
       <c r="T93">
-        <v>9.849478991060176</v>
+        <v>11.0806638649427</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.07673148334510757</v>
+        <v>0.07589744548266074</v>
       </c>
       <c r="W93">
-        <v>0.1853923181443024</v>
+        <v>0.1855597929470817</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.511543222300717</v>
+        <v>0.5059829698844049</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2387763120706942</v>
+        <v>0.2403263120706943</v>
       </c>
       <c r="C94">
-        <v>-157.8923282491234</v>
+        <v>-161.8346741896495</v>
       </c>
       <c r="D94">
-        <v>112.1156717508765</v>
+        <v>111.2223258103505</v>
       </c>
       <c r="E94">
-        <v>141.208</v>
+        <v>144.257</v>
       </c>
       <c r="F94">
-        <v>280.508</v>
+        <v>283.557</v>
       </c>
       <c r="G94">
         <v>10.5</v>
@@ -8995,37 +8995,37 @@
         <v>28.5</v>
       </c>
       <c r="M94">
-        <v>56.3260064</v>
+        <v>56.9382456</v>
       </c>
       <c r="N94">
-        <v>-27.8260064</v>
+        <v>-28.4382456</v>
       </c>
       <c r="O94">
-        <v>-4.173900959999999</v>
+        <v>-4.26573684</v>
       </c>
       <c r="P94">
-        <v>-23.65210544</v>
+        <v>-24.17250876</v>
       </c>
       <c r="Q94">
-        <v>-21.65210544</v>
+        <v>-22.17250876</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8507662819922387</v>
+        <v>0.9657614651339872</v>
       </c>
       <c r="T94">
-        <v>11.0806638649427</v>
+        <v>12.6636158456488</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.07589744548266074</v>
+        <v>0.07508134391833106</v>
       </c>
       <c r="W94">
-        <v>0.1855597929470817</v>
+        <v>0.1857236661411991</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5059829698844049</v>
+        <v>0.5005422927888736</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2403263120706943</v>
+        <v>0.275493846172789</v>
       </c>
       <c r="C95">
-        <v>-161.8346741896495</v>
+        <v>-181.9124932068878</v>
       </c>
       <c r="D95">
-        <v>111.2223258103505</v>
+        <v>94.19350679311218</v>
       </c>
       <c r="E95">
-        <v>144.257</v>
+        <v>147.306</v>
       </c>
       <c r="F95">
-        <v>283.557</v>
+        <v>286.606</v>
       </c>
       <c r="G95">
         <v>10.5</v>
@@ -9077,45 +9077,45 @@
         <v>28.5</v>
       </c>
       <c r="M95">
-        <v>56.9382456</v>
+        <v>67.58169480000001</v>
       </c>
       <c r="N95">
-        <v>-28.4382456</v>
+        <v>-39.08169480000001</v>
       </c>
       <c r="O95">
-        <v>-4.26573684</v>
+        <v>-5.862254220000001</v>
       </c>
       <c r="P95">
-        <v>-24.17250876</v>
+        <v>-33.21944058</v>
       </c>
       <c r="Q95">
-        <v>-22.17250876</v>
+        <v>-31.21944058</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9657614651339872</v>
+        <v>1.131047277691232</v>
       </c>
       <c r="T95">
-        <v>12.6636158456488</v>
+        <v>14.93883726990271</v>
       </c>
       <c r="U95">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07508134391833106</v>
+        <v>0.06325677408137446</v>
       </c>
       <c r="W95">
-        <v>0.1857236661411991</v>
+        <v>0.2208840526716119</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.5005422927888736</v>
+        <v>0.4217118272091631</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.275493846172789</v>
+        <v>0.2773938461727891</v>
       </c>
       <c r="C96">
-        <v>-181.9124932068878</v>
+        <v>-185.7342583984697</v>
       </c>
       <c r="D96">
-        <v>94.19350679311218</v>
+        <v>93.42074160153024</v>
       </c>
       <c r="E96">
-        <v>147.306</v>
+        <v>150.355</v>
       </c>
       <c r="F96">
-        <v>286.606</v>
+        <v>289.655</v>
       </c>
       <c r="G96">
         <v>10.5</v>
@@ -9159,37 +9159,37 @@
         <v>28.5</v>
       </c>
       <c r="M96">
-        <v>67.58169480000001</v>
+        <v>68.30064899999999</v>
       </c>
       <c r="N96">
-        <v>-39.08169480000001</v>
+        <v>-39.80064899999999</v>
       </c>
       <c r="O96">
-        <v>-5.862254220000001</v>
+        <v>-5.970097349999999</v>
       </c>
       <c r="P96">
-        <v>-33.21944058</v>
+        <v>-33.83055165</v>
       </c>
       <c r="Q96">
-        <v>-31.21944058</v>
+        <v>-31.83055165</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.131047277691232</v>
+        <v>1.348096733229479</v>
       </c>
       <c r="T96">
-        <v>14.93883726990271</v>
+        <v>17.92660472388327</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06325677408137446</v>
+        <v>0.06259091330157053</v>
       </c>
       <c r="W96">
-        <v>0.2208840526716119</v>
+        <v>0.2210410626434897</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4217118272091631</v>
+        <v>0.4172727553438036</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2773938461727891</v>
+        <v>0.2792938461727891</v>
       </c>
       <c r="C97">
-        <v>-185.7342583984697</v>
+        <v>-189.5434472083776</v>
       </c>
       <c r="D97">
-        <v>93.42074160153024</v>
+        <v>92.66055279162235</v>
       </c>
       <c r="E97">
-        <v>150.355</v>
+        <v>153.404</v>
       </c>
       <c r="F97">
-        <v>289.655</v>
+        <v>292.704</v>
       </c>
       <c r="G97">
         <v>10.5</v>
@@ -9241,37 +9241,37 @@
         <v>28.5</v>
       </c>
       <c r="M97">
-        <v>68.30064899999999</v>
+        <v>69.01960320000001</v>
       </c>
       <c r="N97">
-        <v>-39.80064899999999</v>
+        <v>-40.51960320000001</v>
       </c>
       <c r="O97">
-        <v>-5.970097349999999</v>
+        <v>-6.077940480000001</v>
       </c>
       <c r="P97">
-        <v>-33.83055165</v>
+        <v>-34.44166272</v>
       </c>
       <c r="Q97">
-        <v>-31.83055165</v>
+        <v>-32.44166272</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.348096733229479</v>
+        <v>1.67367091653685</v>
       </c>
       <c r="T97">
-        <v>17.92660472388327</v>
+        <v>22.40825590485409</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06259091330157053</v>
+        <v>0.06193892462134583</v>
       </c>
       <c r="W97">
-        <v>0.2210410626434897</v>
+        <v>0.2211948015742866</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4172727553438036</v>
+        <v>0.4129261641423055</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.279293846172789</v>
+        <v>0.281193846172789</v>
       </c>
       <c r="C98">
-        <v>-189.5434472083776</v>
+        <v>-193.340364170382</v>
       </c>
       <c r="D98">
-        <v>92.66055279162235</v>
+        <v>91.91263582961798</v>
       </c>
       <c r="E98">
-        <v>153.4039999999999</v>
+        <v>156.453</v>
       </c>
       <c r="F98">
-        <v>292.704</v>
+        <v>295.753</v>
       </c>
       <c r="G98">
         <v>10.5</v>
@@ -9323,37 +9323,37 @@
         <v>28.5</v>
       </c>
       <c r="M98">
-        <v>69.01960319999999</v>
+        <v>69.7385574</v>
       </c>
       <c r="N98">
-        <v>-40.51960319999999</v>
+        <v>-41.2385574</v>
       </c>
       <c r="O98">
-        <v>-6.077940479999999</v>
+        <v>-6.185783610000001</v>
       </c>
       <c r="P98">
-        <v>-34.44166272</v>
+        <v>-35.05277379</v>
       </c>
       <c r="Q98">
-        <v>-32.44166272</v>
+        <v>-33.05277379</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.673670916536845</v>
+        <v>2.21629455538246</v>
       </c>
       <c r="T98">
-        <v>22.40825590485403</v>
+        <v>29.87767453980537</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06193892462134584</v>
+        <v>0.06130037900669278</v>
       </c>
       <c r="W98">
-        <v>0.2211948015742866</v>
+        <v>0.2213453706302218</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4129261641423057</v>
+        <v>0.4086691933779519</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.281193846172789</v>
+        <v>0.283093846172789</v>
       </c>
       <c r="C99">
-        <v>-193.340364170382</v>
+        <v>-197.1253040647066</v>
       </c>
       <c r="D99">
-        <v>91.91263582961798</v>
+        <v>91.1766959352934</v>
       </c>
       <c r="E99">
-        <v>156.453</v>
+        <v>159.502</v>
       </c>
       <c r="F99">
-        <v>295.753</v>
+        <v>298.802</v>
       </c>
       <c r="G99">
         <v>10.5</v>
@@ -9405,37 +9405,37 @@
         <v>28.5</v>
       </c>
       <c r="M99">
-        <v>69.7385574</v>
+        <v>70.45751159999999</v>
       </c>
       <c r="N99">
-        <v>-41.2385574</v>
+        <v>-41.95751159999999</v>
       </c>
       <c r="O99">
-        <v>-6.185783610000001</v>
+        <v>-6.293626739999998</v>
       </c>
       <c r="P99">
-        <v>-35.05277379</v>
+        <v>-35.66388485999999</v>
       </c>
       <c r="Q99">
-        <v>-33.05277379</v>
+        <v>-33.66388485999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.21629455538246</v>
+        <v>3.30154183307369</v>
       </c>
       <c r="T99">
-        <v>29.87767453980537</v>
+        <v>44.81651180970806</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06130037900669278</v>
+        <v>0.06067486493519593</v>
       </c>
       <c r="W99">
-        <v>0.2213453706302218</v>
+        <v>0.2214928668482808</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4086691933779519</v>
+        <v>0.4044990995679729</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.283093846172789</v>
+        <v>0.2849938461727891</v>
       </c>
       <c r="C100">
-        <v>-197.1253040647066</v>
+        <v>-200.8985523054072</v>
       </c>
       <c r="D100">
-        <v>91.1766959352934</v>
+        <v>90.45244769459278</v>
       </c>
       <c r="E100">
-        <v>159.502</v>
+        <v>162.551</v>
       </c>
       <c r="F100">
-        <v>298.802</v>
+        <v>301.851</v>
       </c>
       <c r="G100">
         <v>10.5</v>
@@ -9487,37 +9487,37 @@
         <v>28.5</v>
       </c>
       <c r="M100">
-        <v>70.45751159999999</v>
+        <v>71.1764658</v>
       </c>
       <c r="N100">
-        <v>-41.95751159999999</v>
+        <v>-42.6764658</v>
       </c>
       <c r="O100">
-        <v>-6.293626739999998</v>
+        <v>-6.401469870000001</v>
       </c>
       <c r="P100">
-        <v>-35.66388485999999</v>
+        <v>-36.27499593</v>
       </c>
       <c r="Q100">
-        <v>-33.66388485999999</v>
+        <v>-34.27499593</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.30154183307369</v>
+        <v>6.557283666147381</v>
       </c>
       <c r="T100">
-        <v>44.81651180970806</v>
+        <v>89.63302361941612</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06067486493519593</v>
+        <v>0.06006198751160808</v>
       </c>
       <c r="W100">
-        <v>0.2214928668482808</v>
+        <v>0.2216373833447628</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4044990995679729</v>
+        <v>0.4004132500773873</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2849938461727891</v>
-      </c>
-      <c r="C101">
-        <v>-200.8985523054072</v>
-      </c>
-      <c r="D101">
-        <v>90.45244769459278</v>
-      </c>
-      <c r="E101">
-        <v>162.551</v>
-      </c>
-      <c r="F101">
-        <v>301.851</v>
-      </c>
-      <c r="G101">
-        <v>10.5</v>
-      </c>
-      <c r="H101">
-        <v>165.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>30.5</v>
-      </c>
-      <c r="K101">
-        <v>2</v>
-      </c>
-      <c r="L101">
-        <v>28.5</v>
-      </c>
-      <c r="M101">
-        <v>71.1764658</v>
-      </c>
-      <c r="N101">
-        <v>-42.6764658</v>
-      </c>
-      <c r="O101">
-        <v>-6.401469870000001</v>
-      </c>
-      <c r="P101">
-        <v>-36.27499593</v>
-      </c>
-      <c r="Q101">
-        <v>-34.27499593</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.557283666147381</v>
-      </c>
-      <c r="T101">
-        <v>89.63302361941612</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06006198751160808</v>
-      </c>
-      <c r="W101">
-        <v>0.2216373833447628</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4004132500773873</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
